--- a/slots/resources/sample/condition.xlsx
+++ b/slots/resources/sample/condition.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="75">
   <si>
     <t>id</t>
   </si>
@@ -91,6 +91,9 @@
     <t>levelID</t>
   </si>
   <si>
+    <t>已实现</t>
+  </si>
+  <si>
     <t>开服天数</t>
   </si>
   <si>
@@ -106,13 +109,16 @@
     <t>day</t>
   </si>
   <si>
+    <t>未实现</t>
+  </si>
+  <si>
     <t>个人投注次数</t>
   </si>
   <si>
     <t>BET_COUNT</t>
   </si>
   <si>
-    <t>10001_游戏ID（不区分倍场）_大于等于总押注条件_等于目标投注次数</t>
+    <t>10001_游戏ID_大于等于总押注条件_等于目标投注次数</t>
   </si>
   <si>
     <t>您还未完成任务，请继续游戏</t>
@@ -166,10 +172,88 @@
     <t>个人有效下注</t>
   </si>
   <si>
+    <t>PLAYER_BETALL</t>
+  </si>
+  <si>
+    <t>12001_每累积达到设定有效下注数量（计算所有游戏）</t>
+  </si>
+  <si>
+    <t>bet</t>
+  </si>
+  <si>
     <t>PLAYER_BET</t>
   </si>
   <si>
-    <t>12001_每累积达到设定有效下注数量</t>
+    <t>12002_每累积达到设定有效下注数量（不计算开房间游戏）</t>
+  </si>
+  <si>
+    <t>指定游戏掉落</t>
+  </si>
+  <si>
+    <t>PLAY_GAME</t>
+  </si>
+  <si>
+    <t>12003_每累计达到有效流水时触发|指定范围内游戏可多个游戏_指定范围内游戏可多个游戏</t>
+  </si>
+  <si>
+    <t>bet_gameID</t>
+  </si>
+  <si>
+    <t>Warehouse表中id字段值</t>
+  </si>
+  <si>
+    <t>12003_100_2006001_2006002</t>
+  </si>
+  <si>
+    <t>不在指定游戏掉落</t>
+  </si>
+  <si>
+    <t>NOTPLAY_GAME</t>
+  </si>
+  <si>
+    <t>12004_每累计达到有效流水时触发|排除指定范围内游戏可多个游戏</t>
+  </si>
+  <si>
+    <t>指定游戏类型掉落</t>
+  </si>
+  <si>
+    <t>PLAY_GAMETYPE</t>
+  </si>
+  <si>
+    <t>12005_每累计达到有效流水时触发|指定范围内游戏类型可多个类型</t>
+  </si>
+  <si>
+    <t>bet_gametype</t>
+  </si>
+  <si>
+    <t>Warehouse表中gameType字段值</t>
+  </si>
+  <si>
+    <t>12005_100_1_2</t>
+  </si>
+  <si>
+    <t>只统计1：slot 2：押注类 游戏中的有效流水，每100有效流水触发1次</t>
+  </si>
+  <si>
+    <t>指定房间倍场类型掉落</t>
+  </si>
+  <si>
+    <t>PLAY_ROOMTYPE</t>
+  </si>
+  <si>
+    <t>12005_每累计达到有效流水时触发|指定倍场游戏类型可多个倍场</t>
+  </si>
+  <si>
+    <t>bet_roomtype</t>
+  </si>
+  <si>
+    <t>Warehouse表中roomType字段值</t>
+  </si>
+  <si>
+    <t>12006_100_1_2_3</t>
+  </si>
+  <si>
+    <t>只统计1：基础场 2：中级场 3：高级场 游戏中的有效流水，每100有效流水触发1次</t>
   </si>
 </sst>
 </file>
@@ -354,12 +438,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -680,7 +770,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
@@ -704,16 +794,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="7">
@@ -722,90 +812,93 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
@@ -821,6 +914,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1143,11 +1239,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <dimension ref="A1:O17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="17.125" customWidth="1"/>
-    <col min="3" max="3" width="12.875" customWidth="1"/>
+    <col min="3" max="3" width="19.625" customWidth="1"/>
     <col min="4" max="4" width="20.375" customWidth="1"/>
     <col min="5" max="5" width="49.125" customWidth="1"/>
     <col min="6" max="6" width="21.375" customWidth="1"/>
@@ -1156,19 +1252,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1"/>
+      <c r="E1" s="2"/>
       <c r="F1" t="s">
         <v>4</v>
       </c>
@@ -1180,17 +1276,17 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1" t="s">
+      <c r="E2" s="2"/>
+      <c r="F2" s="2" t="s">
         <v>7</v>
       </c>
       <c r="G2" t="s">
@@ -1201,10 +1297,10 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D3" t="s">
@@ -1220,14 +1316,14 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" ht="17.25" spans="1:8">
+    <row r="5" ht="17.25" spans="1:9">
       <c r="A5">
         <v>1</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D5">
@@ -1236,191 +1332,354 @@
       <c r="E5" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="4">
         <v>48001</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="5" t="s">
         <v>18</v>
       </c>
       <c r="H5" t="s">
         <v>19</v>
       </c>
+      <c r="I5" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="6" ht="17.25" spans="1:8">
+    <row r="6" ht="17.25" spans="1:9">
       <c r="A6">
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="5" t="s">
         <v>21</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="3">
+        <v>23</v>
+      </c>
+      <c r="F6" s="4">
         <v>48002</v>
       </c>
-      <c r="G6" s="4" t="s">
-        <v>23</v>
+      <c r="G6" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="H6" t="s">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="I6" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="7" ht="17.25" spans="1:8">
+    <row r="7" ht="17.25" spans="1:9">
       <c r="A7">
         <v>10001</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>28</v>
       </c>
       <c r="D7">
         <v>3</v>
       </c>
       <c r="E7" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7" s="3">
+        <v>29</v>
+      </c>
+      <c r="F7" s="4">
         <v>48003</v>
       </c>
-      <c r="G7" s="4" t="s">
-        <v>28</v>
+      <c r="G7" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="H7" t="s">
-        <v>29</v>
+        <v>31</v>
+      </c>
+      <c r="I7" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="8" ht="17.25" spans="1:8">
+    <row r="8" ht="17.25" spans="1:9">
       <c r="A8">
         <v>10002</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="D8">
         <v>3</v>
       </c>
       <c r="E8" t="s">
-        <v>32</v>
-      </c>
-      <c r="F8" s="3">
+        <v>34</v>
+      </c>
+      <c r="F8" s="4">
         <v>48003</v>
       </c>
-      <c r="G8" s="4" t="s">
-        <v>28</v>
+      <c r="G8" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="H8" t="s">
-        <v>29</v>
+        <v>31</v>
+      </c>
+      <c r="I8" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="9" ht="17.25" spans="1:8">
+    <row r="9" ht="17.25" spans="1:9">
       <c r="A9">
         <v>10003</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>36</v>
       </c>
       <c r="D9">
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F9" s="3">
+        <v>37</v>
+      </c>
+      <c r="F9" s="4">
         <v>48003</v>
       </c>
-      <c r="G9" s="4" t="s">
-        <v>28</v>
+      <c r="G9" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="H9" t="s">
-        <v>29</v>
+        <v>31</v>
+      </c>
+      <c r="I9" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="10" ht="17.25" spans="1:8">
+    <row r="10" ht="17.25" spans="1:9">
       <c r="A10">
         <v>11001</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>39</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>38</v>
-      </c>
-      <c r="F10" s="3">
+        <v>40</v>
+      </c>
+      <c r="F10" s="4">
         <v>48004</v>
       </c>
-      <c r="G10" s="4" t="s">
-        <v>39</v>
+      <c r="G10" s="5" t="s">
+        <v>41</v>
       </c>
       <c r="H10" t="s">
-        <v>40</v>
+        <v>42</v>
+      </c>
+      <c r="I10" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="11" ht="17.25" spans="1:8">
+    <row r="11" ht="17.25" spans="1:9">
       <c r="A11">
         <v>11002</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>44</v>
       </c>
       <c r="D11">
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>43</v>
-      </c>
-      <c r="F11" s="3">
+        <v>45</v>
+      </c>
+      <c r="F11" s="4">
         <v>48004</v>
       </c>
-      <c r="G11" s="4" t="s">
-        <v>39</v>
+      <c r="G11" s="5" t="s">
+        <v>41</v>
       </c>
       <c r="H11" t="s">
-        <v>40</v>
+        <v>42</v>
+      </c>
+      <c r="I11" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
-      <c r="A12">
+    <row r="12" s="1" customFormat="1" spans="1:9">
+      <c r="A12" s="1">
         <v>12001</v>
       </c>
-      <c r="B12" t="s">
-        <v>44</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12">
+      <c r="B12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="1">
         <v>1</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:9">
+      <c r="A13" s="1">
+        <v>12002</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="C13" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="13" customFormat="1" spans="3:3">
-      <c r="C13" s="5"/>
+    <row r="14" s="1" customFormat="1" spans="1:13">
+      <c r="A14" s="1">
+        <v>12003</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" s="1">
+        <v>2</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:9">
+      <c r="A15" s="1">
+        <v>12004</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="D15" s="1">
+        <v>2</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:15">
+      <c r="A16" s="1">
+        <v>12005</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D16" s="1">
+        <v>2</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:15">
+      <c r="A17" s="1">
+        <v>12006</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D17" s="1">
+        <v>2</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>74</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D5">

--- a/slots/resources/sample/condition.xlsx
+++ b/slots/resources/sample/condition.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="78">
   <si>
     <t>id</t>
   </si>
@@ -118,7 +118,26 @@
     <t>BET_COUNT</t>
   </si>
   <si>
-    <t>10001_游戏ID_大于等于总押注条件_等于目标投注次数</t>
+    <r>
+      <t>10001_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>游戏ID(0 = 任意游戏)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（不区分倍场)_大于等于总押注条件_等于目标投注次数</t>
+    </r>
   </si>
   <si>
     <t>您还未完成任务，请继续游戏</t>
@@ -133,7 +152,26 @@
     <t>PLAYGAME_COUNT</t>
   </si>
   <si>
-    <t>10002_游戏ID（不区分倍场）_大于等于总押注条件_等于目标局数次数</t>
+    <r>
+      <t>10002_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>游戏ID(0 = 任意游戏)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（不区分倍场）_大于等于总押注条件_等于目标局数次数</t>
+    </r>
   </si>
   <si>
     <t>个人游戏实际赢钱</t>
@@ -142,7 +180,35 @@
     <t>PLAYGAME_WINMONEY</t>
   </si>
   <si>
-    <t>10003_游戏ID（不区分倍场）_大于等于总押注条件_大于等于目标获胜金额</t>
+    <r>
+      <t>10003_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>游戏ID(0 = 任意游戏)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（不区分倍场）_大于等于总押注条件_大于等于目标获胜金额</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>_货币ID(金币或钻石)</t>
+    </r>
   </si>
   <si>
     <t>个人单次充值</t>
@@ -151,7 +217,18 @@
     <t>PLAYER_PAY</t>
   </si>
   <si>
-    <t>11001_单次充值大于等于金额</t>
+    <r>
+      <t>11001_单次充值大于等于金额</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>_次数_渠道ID(0=默认所有)</t>
+    </r>
   </si>
   <si>
     <t>您的充值金额不足{0}，请稍后再试</t>
@@ -166,7 +243,18 @@
     <t>PLAYER_SUMPAY</t>
   </si>
   <si>
-    <t>11002_总累计充值大于等于金额</t>
+    <r>
+      <t>11002_总累计充值大于等于金额_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>渠道ID(0=默认所有)</t>
+    </r>
   </si>
   <si>
     <t>个人有效下注</t>
@@ -175,7 +263,26 @@
     <t>PLAYER_BETALL</t>
   </si>
   <si>
-    <t>12001_每累积达到设定有效下注数量（计算所有游戏）</t>
+    <r>
+      <t>12001_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>游戏ID(0 = 任意游戏)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>_每累积达到设定有效下注数量（计算所有游戏）</t>
+    </r>
   </si>
   <si>
     <t>bet</t>
@@ -254,6 +361,15 @@
   </si>
   <si>
     <t>只统计1：基础场 2：中级场 3：高级场 游戏中的有效流水，每100有效流水触发1次</t>
+  </si>
+  <si>
+    <t>累积使用道具数量</t>
+  </si>
+  <si>
+    <t>PLAY_USEITEM</t>
+  </si>
+  <si>
+    <t>12102_道具ID_等于大于目标数量(游戏下注产生的消耗不计算，其它地方都计算 例 系统升级、兑换 )</t>
   </si>
 </sst>
 </file>
@@ -266,16 +382,8 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
+  <fonts count="25">
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -289,8 +397,26 @@
       <charset val="134"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="12"/>
-      <name val="微软雅黑 Light"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
@@ -764,147 +890,153 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -913,10 +1045,25 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1239,283 +1386,285 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:O18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="2" max="2" width="17.125" customWidth="1"/>
-    <col min="3" max="3" width="19.625" customWidth="1"/>
-    <col min="4" max="4" width="20.375" customWidth="1"/>
-    <col min="5" max="5" width="49.125" customWidth="1"/>
-    <col min="6" max="6" width="21.375" customWidth="1"/>
-    <col min="7" max="7" width="38.625" customWidth="1"/>
-    <col min="8" max="8" width="17.125" customWidth="1"/>
+    <col min="1" max="1" width="9" style="2"/>
+    <col min="2" max="2" width="19.5" style="2" customWidth="1"/>
+    <col min="3" max="3" width="19.625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="20.375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="102.375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="21.375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="38.625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="17.125" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2"/>
-      <c r="F1" t="s">
+      <c r="E1" s="4"/>
+      <c r="F1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2" t="s">
+      <c r="E2" s="4"/>
+      <c r="F2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" ht="17.25" spans="1:9">
-      <c r="A5">
+      <c r="A5" s="2">
         <v>1</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="2">
         <v>1</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="3">
         <v>48001</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="5" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="6" ht="17.25" spans="1:9">
-      <c r="A6">
+      <c r="A6" s="2">
         <v>2</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="2">
         <v>1</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="3">
         <v>48002</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" s="5" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="7" ht="17.25" spans="1:9">
-      <c r="A7">
+      <c r="A7" s="2">
         <v>10001</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="2">
         <v>3</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="3">
         <v>48003</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="I7" t="s">
+      <c r="I7" s="5" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="8" ht="17.25" spans="1:9">
-      <c r="A8">
+      <c r="A8" s="2">
         <v>10002</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="2">
         <v>3</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="3">
         <v>48003</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H8" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="I8" t="s">
+      <c r="I8" s="5" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="9" ht="17.25" spans="1:9">
-      <c r="A9">
+      <c r="A9" s="2">
         <v>10003</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D9">
-        <v>3</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="D9" s="10">
+        <v>4</v>
+      </c>
+      <c r="E9" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="3">
         <v>48003</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="G9" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="H9" t="s">
+      <c r="H9" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="I9" t="s">
+      <c r="I9" s="5" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="10" ht="17.25" spans="1:9">
-      <c r="A10">
+      <c r="A10" s="2">
         <v>11001</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="D10" s="10">
+        <v>3</v>
+      </c>
+      <c r="E10" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="3">
         <v>48004</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="G10" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H10" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="I10" t="s">
+      <c r="I10" s="5" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="11" ht="17.25" spans="1:9">
-      <c r="A11">
+      <c r="A11" s="2">
         <v>11002</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="D11" s="10">
+        <v>2</v>
+      </c>
+      <c r="E11" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="3">
         <v>48004</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="G11" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="H11" t="s">
+      <c r="H11" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="I11" t="s">
+      <c r="I11" s="5" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1523,22 +1672,22 @@
       <c r="A12" s="1">
         <v>12001</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="1">
-        <v>1</v>
-      </c>
-      <c r="E12" s="1" t="s">
+      <c r="D12" s="13">
+        <v>2</v>
+      </c>
+      <c r="E12" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="H12" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="I12" s="11" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1546,22 +1695,22 @@
       <c r="A13" s="1">
         <v>12002</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="12" t="s">
         <v>50</v>
       </c>
       <c r="D13" s="1">
         <v>1</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="H13" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="I13" s="1" t="s">
+      <c r="I13" s="11" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1569,28 +1718,28 @@
       <c r="A14" s="1">
         <v>12003</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="12" t="s">
         <v>53</v>
       </c>
       <c r="D14" s="1">
         <v>2</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="H14" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="I14" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="J14" s="1" t="s">
+      <c r="J14" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="M14" s="1" t="s">
+      <c r="M14" s="11" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1598,22 +1747,22 @@
       <c r="A15" s="1">
         <v>12004</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="12" t="s">
         <v>59</v>
       </c>
       <c r="D15" s="1">
         <v>2</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E15" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="H15" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="I15" s="11" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1621,31 +1770,31 @@
       <c r="A16" s="1">
         <v>12005</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="12" t="s">
         <v>62</v>
       </c>
       <c r="D16" s="1">
         <v>2</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="H16" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="I16" s="1" t="s">
+      <c r="I16" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="J16" s="1" t="s">
+      <c r="J16" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="M16" s="1" t="s">
+      <c r="M16" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="O16" s="1" t="s">
+      <c r="O16" s="11" t="s">
         <v>67</v>
       </c>
     </row>
@@ -1653,32 +1802,49 @@
       <c r="A17" s="1">
         <v>12006</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="12" t="s">
         <v>69</v>
       </c>
       <c r="D17" s="1">
         <v>2</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E17" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="H17" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="I17" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="J17" s="1" t="s">
+      <c r="J17" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="M17" s="1" t="s">
+      <c r="M17" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="O17" s="1" t="s">
+      <c r="O17" s="11" t="s">
         <v>74</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="2">
+        <v>12101</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D18" s="2">
+        <v>2</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/condition.xlsx
+++ b/slots/resources/sample/condition.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="80">
   <si>
     <t>id</t>
   </si>
@@ -119,6 +119,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>10001_</t>
     </r>
     <r>
@@ -153,6 +158,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>10002_</t>
     </r>
     <r>
@@ -181,6 +191,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>10003_</t>
     </r>
     <r>
@@ -218,6 +233,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>11001_单次充值大于等于金额</t>
     </r>
     <r>
@@ -264,6 +284,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>12001_</t>
     </r>
     <r>
@@ -348,7 +373,7 @@
     <t>PLAY_ROOMTYPE</t>
   </si>
   <si>
-    <t>12005_每累计达到有效流水时触发|指定倍场游戏类型可多个倍场</t>
+    <t>12006_每累计达到有效流水时触发|指定倍场游戏类型可多个倍场</t>
   </si>
   <si>
     <t>bet_roomtype</t>
@@ -361,6 +386,12 @@
   </si>
   <si>
     <t>只统计1：基础场 2：中级场 3：高级场 游戏中的有效流水，每100有效流水触发1次</t>
+  </si>
+  <si>
+    <t>个人累计有效下注</t>
+  </si>
+  <si>
+    <t>12007_总累计达到设定有效下注数量（不计算开房间游戏）</t>
   </si>
   <si>
     <t>累积使用道具数量</t>
@@ -1020,7 +1051,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1031,12 +1062,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1052,9 +1077,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1386,7 +1408,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -1400,7 +1422,7 @@
     <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:15">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1413,356 +1435,356 @@
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4"/>
-      <c r="F1" s="5" t="s">
+      <c r="E1" s="3"/>
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:15">
       <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="4"/>
+      <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:15">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" ht="17.25" spans="1:9">
+    <row r="5" ht="17.25" spans="1:15">
       <c r="A5" s="2">
         <v>1</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="4" t="s">
         <v>16</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F5" s="3">
         <v>48001</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="6" ht="17.25" spans="1:9">
+    <row r="6" ht="17.25" spans="1:15">
       <c r="A6" s="2">
         <v>2</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="6" t="s">
         <v>22</v>
       </c>
       <c r="D6" s="2">
         <v>1</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="2" t="s">
         <v>23</v>
       </c>
       <c r="F6" s="3">
         <v>48002</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="I6" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="7" ht="17.25" spans="1:9">
+    <row r="7" ht="17.25" spans="1:15">
       <c r="A7" s="2">
         <v>10001</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D7" s="2">
         <v>3</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F7" s="3">
         <v>48003</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="H7" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="I7" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="8" ht="17.25" spans="1:9">
+    <row r="8" ht="17.25" spans="1:15">
       <c r="A8" s="2">
         <v>10002</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="6" t="s">
         <v>33</v>
       </c>
       <c r="D8" s="2">
         <v>3</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="7" t="s">
         <v>34</v>
       </c>
       <c r="F8" s="3">
         <v>48003</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="I8" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="9" ht="17.25" spans="1:9">
+    <row r="9" ht="17.25" spans="1:15">
       <c r="A9" s="2">
         <v>10003</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="8">
         <v>4</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="7" t="s">
         <v>37</v>
       </c>
       <c r="F9" s="3">
         <v>48003</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G9" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H9" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="I9" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="10" ht="17.25" spans="1:9">
+    <row r="10" ht="17.25" spans="1:15">
       <c r="A10" s="2">
         <v>11001</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="8">
         <v>3</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" s="7" t="s">
         <v>40</v>
       </c>
       <c r="F10" s="3">
         <v>48004</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G10" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="H10" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="I10" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="11" ht="17.25" spans="1:9">
+    <row r="11" ht="17.25" spans="1:15">
       <c r="A11" s="2">
         <v>11002</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="8">
         <v>2</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E11" s="7" t="s">
         <v>45</v>
       </c>
       <c r="F11" s="3">
         <v>48004</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H11" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I11" s="5" t="s">
+      <c r="I11" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" spans="1:9">
+    <row r="12" s="1" customFormat="1" spans="1:15">
       <c r="A12" s="1">
         <v>12001</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="13">
+      <c r="D12" s="10">
         <v>2</v>
       </c>
-      <c r="E12" s="14" t="s">
+      <c r="E12" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="H12" s="11" t="s">
+      <c r="H12" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="I12" s="11" t="s">
+      <c r="I12" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" spans="1:9">
+    <row r="13" s="1" customFormat="1" spans="1:15">
       <c r="A13" s="1">
         <v>12002</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="9" t="s">
         <v>50</v>
       </c>
       <c r="D13" s="1">
         <v>1</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="E13" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="H13" s="11" t="s">
+      <c r="H13" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="I13" s="11" t="s">
+      <c r="I13" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" spans="1:13">
+    <row r="14" s="1" customFormat="1" spans="1:15">
       <c r="A14" s="1">
         <v>12003</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="9" t="s">
         <v>53</v>
       </c>
       <c r="D14" s="1">
         <v>2</v>
       </c>
-      <c r="E14" s="14" t="s">
+      <c r="E14" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="H14" s="11" t="s">
+      <c r="H14" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="I14" s="11" t="s">
+      <c r="I14" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="J14" s="11" t="s">
+      <c r="J14" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="M14" s="11" t="s">
+      <c r="M14" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" spans="1:9">
+    <row r="15" s="1" customFormat="1" spans="1:15">
       <c r="A15" s="1">
         <v>12004</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="9" t="s">
         <v>59</v>
       </c>
       <c r="D15" s="1">
         <v>2</v>
       </c>
-      <c r="E15" s="14" t="s">
+      <c r="E15" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="H15" s="11" t="s">
+      <c r="H15" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="I15" s="11" t="s">
+      <c r="I15" s="1" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1770,31 +1792,31 @@
       <c r="A16" s="1">
         <v>12005</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="9" t="s">
         <v>62</v>
       </c>
       <c r="D16" s="1">
         <v>2</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="E16" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="H16" s="11" t="s">
+      <c r="H16" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="I16" s="11" t="s">
+      <c r="I16" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="J16" s="11" t="s">
+      <c r="J16" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="M16" s="11" t="s">
+      <c r="M16" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="O16" s="11" t="s">
+      <c r="O16" s="1" t="s">
         <v>67</v>
       </c>
     </row>
@@ -1802,49 +1824,70 @@
       <c r="A17" s="1">
         <v>12006</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="9" t="s">
         <v>69</v>
       </c>
       <c r="D17" s="1">
         <v>2</v>
       </c>
-      <c r="E17" s="11" t="s">
+      <c r="E17" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H17" s="11" t="s">
+      <c r="H17" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="I17" s="11" t="s">
+      <c r="I17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="J17" s="11" t="s">
+      <c r="J17" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="M17" s="11" t="s">
+      <c r="M17" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="O17" s="11" t="s">
+      <c r="O17" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="2">
+    <row r="18" s="1" customFormat="1" spans="1:15">
+      <c r="A18" s="1">
+        <v>12007</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C18" s="9"/>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
+      <c r="A19" s="2">
         <v>12101</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D18" s="2">
+      <c r="B19" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D19" s="2">
         <v>2</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>77</v>
+      <c r="E19" s="2" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/condition.xlsx
+++ b/slots/resources/sample/condition.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="85">
   <si>
     <t>id</t>
   </si>
@@ -110,6 +110,21 @@
   </si>
   <si>
     <t>未实现</t>
+  </si>
+  <si>
+    <t>VIP等级条件</t>
+  </si>
+  <si>
+    <t>PLAYER_VIPLEVEL</t>
+  </si>
+  <si>
+    <t>1_大于等于玩家VIP等级</t>
+  </si>
+  <si>
+    <t>您的VIP不足{0}級，請提升VIP等級後再試</t>
+  </si>
+  <si>
+    <t>VIPlevelID</t>
   </si>
   <si>
     <t>个人投注次数</t>
@@ -264,6 +279,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>11002_总累计充值大于等于金额_</t>
     </r>
     <r>
@@ -1408,7 +1428,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -1422,7 +1442,7 @@
     <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:13">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1446,7 +1466,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:13">
       <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
@@ -1467,7 +1487,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:13">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1487,7 +1507,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" ht="17.25" spans="1:15">
+    <row r="5" ht="17.25" spans="1:13">
       <c r="A5" s="2">
         <v>1</v>
       </c>
@@ -1516,7 +1536,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" ht="17.25" spans="1:15">
+    <row r="6" ht="17.25" spans="1:13">
       <c r="A6" s="2">
         <v>2</v>
       </c>
@@ -1545,24 +1565,24 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" ht="17.25" spans="1:15">
+    <row r="7" ht="17.25" spans="1:13">
       <c r="A7" s="2">
-        <v>10001</v>
+        <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="4" t="s">
         <v>28</v>
       </c>
       <c r="D7" s="2">
-        <v>3</v>
-      </c>
-      <c r="E7" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>29</v>
       </c>
       <c r="F7" s="3">
-        <v>48003</v>
+        <v>48001</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>30</v>
@@ -1571,12 +1591,12 @@
         <v>31</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="8" ht="17.25" spans="1:15">
+    <row r="8" ht="17.25" spans="1:13">
       <c r="A8" s="2">
-        <v>10002</v>
+        <v>10001</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>32</v>
@@ -1594,76 +1614,76 @@
         <v>48003</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="9" ht="17.25" spans="1:15">
+    <row r="9" ht="17.25" spans="1:13">
       <c r="A9" s="2">
-        <v>10003</v>
+        <v>10002</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" s="8">
-        <v>4</v>
+        <v>38</v>
+      </c>
+      <c r="D9" s="2">
+        <v>3</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F9" s="3">
         <v>48003</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="10" ht="17.25" spans="1:15">
+    <row r="10" ht="17.25" spans="1:13">
       <c r="A10" s="2">
-        <v>11001</v>
+        <v>10003</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D10" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F10" s="3">
-        <v>48004</v>
+        <v>48003</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="11" ht="17.25" spans="1:15">
+    <row r="11" ht="17.25" spans="1:13">
       <c r="A11" s="2">
-        <v>11002</v>
+        <v>11001</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>43</v>
@@ -1672,7 +1692,7 @@
         <v>44</v>
       </c>
       <c r="D11" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>45</v>
@@ -1681,220 +1701,252 @@
         <v>48004</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" spans="1:15">
-      <c r="A12" s="1">
+    <row r="12" ht="17.25" spans="1:13">
+      <c r="A12" s="2">
+        <v>11002</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="8">
+        <v>2</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F12" s="3">
+        <v>48004</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:13">
+      <c r="A13" s="1">
         <v>12001</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="D12" s="10">
+      <c r="B13" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" s="10">
         <v>2</v>
       </c>
-      <c r="E12" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" spans="1:15">
-      <c r="A13" s="1">
-        <v>12002</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="D13" s="1">
-        <v>1</v>
-      </c>
       <c r="E13" s="11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" spans="1:15">
+    <row r="14" s="1" customFormat="1" spans="1:13">
       <c r="A14" s="1">
-        <v>12003</v>
+        <v>12002</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D14" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="H14" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>55</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="J14" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="M14" s="1" t="s">
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:13">
+      <c r="A15" s="1">
+        <v>12003</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="15" s="1" customFormat="1" spans="1:15">
-      <c r="A15" s="1">
-        <v>12004</v>
-      </c>
-      <c r="B15" s="1" t="s">
+      <c r="C15" s="9" t="s">
         <v>58</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>59</v>
       </c>
       <c r="D15" s="1">
         <v>2</v>
       </c>
       <c r="E15" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="H15" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>55</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>26</v>
       </c>
+      <c r="J15" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>62</v>
+      </c>
     </row>
-    <row r="16" s="1" customFormat="1" spans="1:15">
+    <row r="16" s="1" customFormat="1" spans="1:13">
       <c r="A16" s="1">
-        <v>12005</v>
+        <v>12004</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D16" s="1">
         <v>2</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>63</v>
+      <c r="E16" s="11" t="s">
+        <v>65</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="M16" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="O16" s="1" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" spans="1:15">
       <c r="A17" s="1">
-        <v>12006</v>
+        <v>12005</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D17" s="1">
         <v>2</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>26</v>
       </c>
       <c r="J17" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="O17" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="M17" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="O17" s="1" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" spans="1:15">
       <c r="A18" s="1">
-        <v>12007</v>
+        <v>12006</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D18" s="1">
+        <v>2</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C18" s="9"/>
-      <c r="D18" s="1">
-        <v>1</v>
-      </c>
-      <c r="E18" s="11" t="s">
+      <c r="H18" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>49</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>26</v>
       </c>
+      <c r="J18" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>79</v>
+      </c>
     </row>
-    <row r="19" spans="1:15">
-      <c r="A19" s="2">
+    <row r="19" s="1" customFormat="1" spans="1:15">
+      <c r="A19" s="1">
+        <v>12007</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C19" s="9"/>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
+      <c r="A20" s="2">
         <v>12101</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D19" s="2">
+      <c r="B20" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D20" s="2">
         <v>2</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>79</v>
+      <c r="E20" s="2" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D5">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D6">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D6">
+  <conditionalFormatting sqref="D7">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/condition.xlsx
+++ b/slots/resources/sample/condition.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="90">
   <si>
     <t>id</t>
   </si>
@@ -118,13 +118,28 @@
     <t>PLAYER_VIPLEVEL</t>
   </si>
   <si>
-    <t>1_大于等于玩家VIP等级</t>
+    <t>3_大于等于玩家VIP等级</t>
   </si>
   <si>
     <t>您的VIP不足{0}級，請提升VIP等級後再試</t>
   </si>
   <si>
     <t>VIPlevelID</t>
+  </si>
+  <si>
+    <t>需要绑定手机</t>
+  </si>
+  <si>
+    <t>PLAYER_PHONE</t>
+  </si>
+  <si>
+    <t>4_1(需要绑定手机）</t>
+  </si>
+  <si>
+    <t>您尚未绑定手机，精绑定手机号后再试</t>
+  </si>
+  <si>
+    <t>playerPhone</t>
   </si>
   <si>
     <t>个人投注次数</t>
@@ -615,12 +630,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -947,7 +968,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
@@ -971,16 +992,16 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="6">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="7">
@@ -989,93 +1010,96 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1093,19 +1117,25 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1428,525 +1458,557 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O20"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="9" style="2"/>
-    <col min="2" max="2" width="19.5" style="2" customWidth="1"/>
-    <col min="3" max="3" width="19.625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="20.375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="102.375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="21.375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="38.625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="17.125" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="9" style="3"/>
+    <col min="2" max="2" width="19.5" style="3" customWidth="1"/>
+    <col min="3" max="3" width="19.625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="17.6416666666667" style="3" customWidth="1"/>
+    <col min="5" max="5" width="27.7916666666667" style="3" customWidth="1"/>
+    <col min="6" max="6" width="21.375" style="3" customWidth="1"/>
+    <col min="7" max="7" width="38.625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="17.125" style="3" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3"/>
-      <c r="F1" s="2" t="s">
+      <c r="E1" s="4"/>
+      <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3" t="s">
+      <c r="E2" s="4"/>
+      <c r="F2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" ht="17.25" spans="1:13">
-      <c r="A5" s="2">
+      <c r="A5" s="3">
         <v>1</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="3">
         <v>1</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="4">
         <v>48001</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="I5" s="3" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="6" ht="17.25" spans="1:13">
-      <c r="A6" s="2">
+      <c r="A6" s="3">
         <v>2</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="3">
         <v>1</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="4">
         <v>48002</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="I6" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="7" ht="17.25" spans="1:13">
-      <c r="A7" s="2">
+      <c r="A7" s="3">
         <v>3</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="3">
         <v>1</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="4">
         <v>48001</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="I7" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" ht="17.25" spans="1:13">
-      <c r="A8" s="2">
-        <v>10001</v>
-      </c>
-      <c r="B8" s="2" t="s">
+    <row r="8" s="1" customFormat="1" ht="17.25" spans="1:13">
+      <c r="A8" s="1">
+        <v>4</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="2">
-        <v>3</v>
-      </c>
-      <c r="E8" s="7" t="s">
+      <c r="D8" s="3">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F8" s="3">
-        <v>48003</v>
-      </c>
-      <c r="G8" s="5" t="s">
+      <c r="F8" s="8">
+        <v>48005</v>
+      </c>
+      <c r="G8" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="H8" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I8" s="2" t="s">
-        <v>26</v>
+      <c r="I8" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="9" ht="17.25" spans="1:13">
-      <c r="A9" s="2">
-        <v>10002</v>
-      </c>
-      <c r="B9" s="2" t="s">
+      <c r="A9" s="3">
+        <v>10001</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="3">
         <v>3</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="4">
         <v>48003</v>
       </c>
-      <c r="G9" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I9" s="2" t="s">
+      <c r="G9" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="10" ht="17.25" spans="1:13">
-      <c r="A10" s="2">
-        <v>10003</v>
-      </c>
-      <c r="B10" s="2" t="s">
+      <c r="A10" s="3">
+        <v>10002</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="3">
+        <v>3</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10" s="4">
+        <v>48003</v>
+      </c>
+      <c r="G10" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="H10" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="8">
-        <v>4</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="F10" s="3">
-        <v>48003</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I10" s="2" t="s">
+      <c r="I10" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="11" ht="17.25" spans="1:13">
-      <c r="A11" s="2">
-        <v>11001</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="D11" s="8">
-        <v>3</v>
-      </c>
-      <c r="E11" s="7" t="s">
+      <c r="A11" s="3">
+        <v>10003</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F11" s="3">
-        <v>48004</v>
-      </c>
-      <c r="G11" s="5" t="s">
+      <c r="C11" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="D11" s="11">
+        <v>4</v>
+      </c>
+      <c r="E11" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="F11" s="4">
+        <v>48003</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="12" ht="17.25" spans="1:13">
-      <c r="A12" s="2">
+      <c r="A12" s="3">
+        <v>11001</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="11">
+        <v>3</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="F12" s="4">
+        <v>48004</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" ht="17.25" spans="1:13">
+      <c r="A13" s="3">
         <v>11002</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D12" s="8">
+      <c r="B13" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" s="11">
         <v>2</v>
       </c>
-      <c r="E12" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="F12" s="3">
+      <c r="E13" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" s="4">
         <v>48004</v>
       </c>
-      <c r="G12" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="I12" s="2" t="s">
+      <c r="G13" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" spans="1:13">
-      <c r="A13" s="1">
+    <row r="14" s="2" customFormat="1" spans="1:13">
+      <c r="A14" s="2">
         <v>12001</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13" s="10">
+      <c r="B14" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" s="13">
         <v>2</v>
       </c>
-      <c r="E13" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>26</v>
+      <c r="E14" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" spans="1:13">
-      <c r="A14" s="1">
+    <row r="15" s="2" customFormat="1" spans="1:13">
+      <c r="A15" s="2">
         <v>12002</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="D14" s="1">
+      <c r="B15" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="D15" s="2">
         <v>1</v>
       </c>
-      <c r="E14" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>26</v>
+      <c r="E15" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" spans="1:13">
-      <c r="A15" s="1">
+    <row r="16" s="2" customFormat="1" spans="1:13">
+      <c r="A16" s="2">
         <v>12003</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="D15" s="1">
+      <c r="B16" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="D16" s="2">
         <v>2</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="E16" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="1" spans="1:15">
+      <c r="A17" s="2">
+        <v>12004</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="D17" s="2">
+        <v>2</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" s="2" customFormat="1" spans="1:15">
+      <c r="A18" s="2">
+        <v>12005</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="D18" s="2">
+        <v>2</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" spans="1:15">
+      <c r="A19" s="2">
+        <v>12006</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="D19" s="2">
+        <v>2</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1" spans="1:15">
+      <c r="A20" s="2">
+        <v>12007</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C20" s="12"/>
+      <c r="D20" s="2">
+        <v>1</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="H20" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="H15" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>62</v>
+      <c r="I20" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" spans="1:13">
-      <c r="A16" s="1">
-        <v>12004</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="D16" s="1">
+    <row r="21" spans="1:15">
+      <c r="A21" s="3">
+        <v>12101</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D21" s="3">
         <v>2</v>
       </c>
-      <c r="E16" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="1:15">
-      <c r="A17" s="1">
-        <v>12005</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D17" s="1">
-        <v>2</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="M17" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="O17" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" spans="1:15">
-      <c r="A18" s="1">
-        <v>12006</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="D18" s="1">
-        <v>2</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="M18" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="O18" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" spans="1:15">
-      <c r="A19" s="1">
-        <v>12007</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C19" s="9"/>
-      <c r="D19" s="1">
-        <v>1</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15">
-      <c r="A20" s="2">
-        <v>12101</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D20" s="2">
-        <v>2</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>84</v>
+      <c r="E21" s="3" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D5">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D6">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D6">
+  <conditionalFormatting sqref="D7">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D7">
+  <conditionalFormatting sqref="D8">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/condition.xlsx
+++ b/slots/resources/sample/condition.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="96">
   <si>
     <t>id</t>
   </si>
@@ -79,7 +79,7 @@
     <t>等级条件</t>
   </si>
   <si>
-    <t>PLAYER_LEVEL</t>
+    <t>playerLevel</t>
   </si>
   <si>
     <t>1_大于等于玩家等级</t>
@@ -97,7 +97,7 @@
     <t>开服天数</t>
   </si>
   <si>
-    <t>OPEN_SERVERDAY</t>
+    <t>openServerDay</t>
   </si>
   <si>
     <t>2_大于等于天数（1表示第一天）</t>
@@ -115,7 +115,7 @@
     <t>VIP等级条件</t>
   </si>
   <si>
-    <t>PLAYER_VIPLEVEL</t>
+    <t>playerVipLevel</t>
   </si>
   <si>
     <t>3_大于等于玩家VIP等级</t>
@@ -130,7 +130,7 @@
     <t>需要绑定手机</t>
   </si>
   <si>
-    <t>PLAYER_PHONE</t>
+    <t>bindPhone</t>
   </si>
   <si>
     <t>4_1(需要绑定手机）</t>
@@ -145,7 +145,7 @@
     <t>个人投注次数</t>
   </si>
   <si>
-    <t>BET_COUNT</t>
+    <t>betFrequency</t>
   </si>
   <si>
     <r>
@@ -184,7 +184,7 @@
     <t>个人游戏次数</t>
   </si>
   <si>
-    <t>PLAYGAME_COUNT</t>
+    <t>playGameCount</t>
   </si>
   <si>
     <r>
@@ -217,7 +217,7 @@
     <t>个人游戏实际赢钱</t>
   </si>
   <si>
-    <t>PLAYGAME_WINMONEY</t>
+    <t>playGameWinMoney</t>
   </si>
   <si>
     <r>
@@ -259,7 +259,7 @@
     <t>个人单次充值</t>
   </si>
   <si>
-    <t>PLAYER_PAY</t>
+    <t>singleRecharge</t>
   </si>
   <si>
     <r>
@@ -290,7 +290,7 @@
     <t>个人累计充值</t>
   </si>
   <si>
-    <t>PLAYER_SUMPAY</t>
+    <t>totalRecharge</t>
   </si>
   <si>
     <r>
@@ -312,10 +312,41 @@
     </r>
   </si>
   <si>
+    <t>个人今日累计充值</t>
+  </si>
+  <si>
+    <t>todayDeposit</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>11003_当日累计充值大于等于金额_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>渠道ID(0=默认所有)</t>
+    </r>
+  </si>
+  <si>
+    <t>您今日的充值金额不足{0}，请稍后再试</t>
+  </si>
+  <si>
+    <t>AND(LEVEL(30), LEVEL(40))，or,not</t>
+  </si>
+  <si>
     <t>个人有效下注</t>
   </si>
   <si>
-    <t>PLAYER_BETALL</t>
+    <t>effectiveBetAll</t>
   </si>
   <si>
     <r>
@@ -348,7 +379,7 @@
     <t>bet</t>
   </si>
   <si>
-    <t>PLAYER_BET</t>
+    <t>effectiveBet</t>
   </si>
   <si>
     <t>12002_每累积达到设定有效下注数量（不计算开房间游戏）</t>
@@ -357,7 +388,7 @@
     <t>指定游戏掉落</t>
   </si>
   <si>
-    <t>PLAY_GAME</t>
+    <t>gameIdDorp</t>
   </si>
   <si>
     <t>12003_每累计达到有效流水时触发|指定范围内游戏可多个游戏_指定范围内游戏可多个游戏</t>
@@ -375,7 +406,7 @@
     <t>不在指定游戏掉落</t>
   </si>
   <si>
-    <t>NOTPLAY_GAME</t>
+    <t>gameIdNotDorp</t>
   </si>
   <si>
     <t>12004_每累计达到有效流水时触发|排除指定范围内游戏可多个游戏</t>
@@ -384,7 +415,7 @@
     <t>指定游戏类型掉落</t>
   </si>
   <si>
-    <t>PLAY_GAMETYPE</t>
+    <t>gameTypeDrop</t>
   </si>
   <si>
     <t>12005_每累计达到有效流水时触发|指定范围内游戏类型可多个类型</t>
@@ -405,7 +436,7 @@
     <t>指定房间倍场类型掉落</t>
   </si>
   <si>
-    <t>PLAY_ROOMTYPE</t>
+    <t>gameRoomTypeDrop</t>
   </si>
   <si>
     <t>12006_每累计达到有效流水时触发|指定倍场游戏类型可多个倍场</t>
@@ -426,13 +457,16 @@
     <t>个人累计有效下注</t>
   </si>
   <si>
+    <t>totalValidBets</t>
+  </si>
+  <si>
     <t>12007_总累计达到设定有效下注数量（不计算开房间游戏）</t>
   </si>
   <si>
     <t>累积使用道具数量</t>
   </si>
   <si>
-    <t>PLAY_USEITEM</t>
+    <t>useItemCount</t>
   </si>
   <si>
     <t>12102_道具ID_等于大于目标数量(游戏下注产生的消耗不计算，其它地方都计算 例 系统升级、兑换 )</t>
@@ -630,7 +664,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -645,7 +679,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.8"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -766,12 +800,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -947,152 +975,152 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1108,15 +1136,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -1129,7 +1154,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1458,21 +1483,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
     <col min="2" max="2" width="19.5" style="3" customWidth="1"/>
     <col min="3" max="3" width="19.625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="17.6416666666667" style="3" customWidth="1"/>
-    <col min="5" max="5" width="27.7916666666667" style="3" customWidth="1"/>
+    <col min="4" max="4" width="17.625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="45.1416666666667" style="3" customWidth="1"/>
     <col min="6" max="6" width="21.375" style="3" customWidth="1"/>
     <col min="7" max="7" width="38.625" style="3" customWidth="1"/>
     <col min="8" max="8" width="17.125" style="3" customWidth="1"/>
     <col min="9" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:10">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1496,7 +1521,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:10">
       <c r="A2" s="4" t="s">
         <v>7</v>
       </c>
@@ -1517,7 +1542,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:10">
       <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
@@ -1537,7 +1562,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" ht="17.25" spans="1:13">
+    <row r="5" ht="17.25" spans="1:10">
       <c r="A5" s="3">
         <v>1</v>
       </c>
@@ -1566,14 +1591,14 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" ht="17.25" spans="1:13">
+    <row r="6" ht="17.25" spans="1:10">
       <c r="A6" s="3">
         <v>2</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="5" t="s">
         <v>22</v>
       </c>
       <c r="D6" s="3">
@@ -1595,7 +1620,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" ht="17.25" spans="1:13">
+    <row r="7" ht="17.25" spans="1:10">
       <c r="A7" s="3">
         <v>3</v>
       </c>
@@ -1624,7 +1649,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="17.25" spans="1:13">
+    <row r="8" s="1" customFormat="1" ht="17.25" spans="1:10">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -1640,10 +1665,10 @@
       <c r="E8" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="7">
         <v>48005</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="G8" s="8" t="s">
         <v>35</v>
       </c>
       <c r="H8" s="1" t="s">
@@ -1653,20 +1678,20 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" ht="17.25" spans="1:13">
+    <row r="9" ht="17.25" spans="1:10">
       <c r="A9" s="3">
         <v>10001</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D9" s="3">
         <v>3</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="9" t="s">
         <v>39</v>
       </c>
       <c r="F9" s="4">
@@ -1682,20 +1707,20 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" ht="17.25" spans="1:13">
+    <row r="10" ht="17.25" spans="1:10">
       <c r="A10" s="3">
         <v>10002</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="5" t="s">
         <v>43</v>
       </c>
       <c r="D10" s="3">
         <v>3</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="9" t="s">
         <v>44</v>
       </c>
       <c r="F10" s="4">
@@ -1711,20 +1736,20 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" ht="17.25" spans="1:13">
+    <row r="11" ht="17.25" spans="1:10">
       <c r="A11" s="3">
         <v>10003</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="10">
         <v>4</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F11" s="4">
@@ -1740,20 +1765,20 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" ht="17.25" spans="1:13">
+    <row r="12" ht="17.25" spans="1:10">
       <c r="A12" s="3">
         <v>11001</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="10">
         <v>3</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="9" t="s">
         <v>50</v>
       </c>
       <c r="F12" s="4">
@@ -1769,20 +1794,20 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" ht="17.25" spans="1:13">
+    <row r="13" ht="17.25" spans="1:10">
       <c r="A13" s="3">
         <v>11002</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="10">
         <v>2</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="E13" s="9" t="s">
         <v>55</v>
       </c>
       <c r="F13" s="4">
@@ -1798,204 +1823,238 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" s="2" customFormat="1" spans="1:13">
-      <c r="A14" s="2">
-        <v>12001</v>
-      </c>
-      <c r="B14" s="2" t="s">
+    <row r="14" ht="17.25" spans="1:10">
+      <c r="A14" s="3">
+        <v>11003</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="13">
+      <c r="D14" s="10">
         <v>2</v>
       </c>
-      <c r="E14" s="14" t="s">
+      <c r="E14" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="F14" s="7">
+        <v>48006</v>
+      </c>
+      <c r="G14" s="6" t="s">
         <v>59</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>52</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>20</v>
       </c>
+      <c r="J14" s="11" t="s">
+        <v>60</v>
+      </c>
     </row>
-    <row r="15" s="2" customFormat="1" spans="1:13">
+    <row r="15" s="2" customFormat="1" spans="1:10">
       <c r="A15" s="2">
-        <v>12002</v>
+        <v>12001</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="D15" s="2">
-        <v>1</v>
-      </c>
-      <c r="E15" s="14" t="s">
         <v>61</v>
       </c>
+      <c r="C15" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D15" s="12">
+        <v>2</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>63</v>
+      </c>
       <c r="H15" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="16" s="2" customFormat="1" spans="1:13">
+    <row r="16" s="2" customFormat="1" spans="1:10">
       <c r="A16" s="2">
-        <v>12003</v>
+        <v>12002</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>63</v>
+        <v>61</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>65</v>
       </c>
       <c r="D16" s="2">
-        <v>2</v>
-      </c>
-      <c r="E16" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>65</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" spans="1:15">
       <c r="A17" s="2">
-        <v>12004</v>
+        <v>12003</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>68</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>69</v>
       </c>
       <c r="D17" s="2">
         <v>2</v>
       </c>
-      <c r="E17" s="14" t="s">
+      <c r="E17" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>65</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>20</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" spans="1:15">
       <c r="A18" s="2">
-        <v>12005</v>
+        <v>12004</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>74</v>
       </c>
       <c r="D18" s="2">
         <v>2</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>73</v>
+      <c r="E18" s="13" t="s">
+        <v>75</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="O18" s="2" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" spans="1:15">
       <c r="A19" s="2">
-        <v>12006</v>
+        <v>12005</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>79</v>
+        <v>76</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>77</v>
       </c>
       <c r="D19" s="2">
         <v>2</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>20</v>
       </c>
       <c r="J19" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="O19" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="O19" s="2" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" spans="1:15">
       <c r="A20" s="2">
-        <v>12007</v>
+        <v>12006</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D20" s="2">
+        <v>2</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C20" s="12"/>
-      <c r="D20" s="2">
-        <v>1</v>
-      </c>
-      <c r="E20" s="14" t="s">
+      <c r="H20" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>20</v>
       </c>
+      <c r="J20" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>89</v>
+      </c>
     </row>
-    <row r="21" spans="1:15">
-      <c r="A21" s="3">
+    <row r="21" s="2" customFormat="1" spans="1:15">
+      <c r="A21" s="2">
+        <v>12007</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D21" s="2">
+        <v>1</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15">
+      <c r="A22" s="3">
         <v>12101</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="D21" s="3">
+      <c r="B22" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D22" s="3">
         <v>2</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>89</v>
+      <c r="E22" s="3" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/condition.xlsx
+++ b/slots/resources/sample/condition.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="condition" sheetId="1" r:id="rId1"/>
@@ -28,8 +28,40 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Administrator</author>
+  </authors>
+  <commentList>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+首字母小写</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="99">
   <si>
     <t>id</t>
   </si>
@@ -140,6 +172,15 @@
   </si>
   <si>
     <t>playerPhone</t>
+  </si>
+  <si>
+    <t>活动剩余参与次数</t>
+  </si>
+  <si>
+    <t>remainingAttempts</t>
+  </si>
+  <si>
+    <t>remainingAttempts(activity表中的ID,剩余次数)</t>
   </si>
   <si>
     <t>个人投注次数</t>
@@ -482,7 +523,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -505,6 +546,12 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF7030A0"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -662,6 +709,17 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="34">
@@ -990,137 +1048,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1148,19 +1206,22 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1483,7 +1544,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O22"/>
+  <dimension ref="A1:O23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -1678,59 +1739,52 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" ht="17.25" spans="1:10">
-      <c r="A9" s="3">
-        <v>10001</v>
-      </c>
-      <c r="B9" s="3" t="s">
+    <row r="9" s="1" customFormat="1" ht="17.25" spans="1:10">
+      <c r="A9" s="1">
+        <v>5</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D9" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F9" s="4">
-        <v>48003</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>41</v>
-      </c>
+      <c r="F9" s="7"/>
+      <c r="G9" s="8"/>
       <c r="I9" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" ht="17.25" spans="1:10">
       <c r="A10" s="3">
-        <v>10002</v>
+        <v>10001</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D10" s="3">
         <v>3</v>
       </c>
-      <c r="E10" s="9" t="s">
-        <v>44</v>
+      <c r="E10" s="10" t="s">
+        <v>42</v>
       </c>
       <c r="F10" s="4">
         <v>48003</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>26</v>
@@ -1738,7 +1792,7 @@
     </row>
     <row r="11" ht="17.25" spans="1:10">
       <c r="A11" s="3">
-        <v>10003</v>
+        <v>10002</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>45</v>
@@ -1746,20 +1800,20 @@
       <c r="C11" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="D11" s="10">
-        <v>4</v>
-      </c>
-      <c r="E11" s="9" t="s">
+      <c r="D11" s="3">
+        <v>3</v>
+      </c>
+      <c r="E11" s="10" t="s">
         <v>47</v>
       </c>
       <c r="F11" s="4">
         <v>48003</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>26</v>
@@ -1767,7 +1821,7 @@
     </row>
     <row r="12" ht="17.25" spans="1:10">
       <c r="A12" s="3">
-        <v>11001</v>
+        <v>10003</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>48</v>
@@ -1775,20 +1829,20 @@
       <c r="C12" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D12" s="10">
-        <v>3</v>
-      </c>
-      <c r="E12" s="9" t="s">
+      <c r="D12" s="11">
+        <v>4</v>
+      </c>
+      <c r="E12" s="10" t="s">
         <v>50</v>
       </c>
       <c r="F12" s="4">
-        <v>48004</v>
+        <v>48003</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>26</v>
@@ -1796,28 +1850,28 @@
     </row>
     <row r="13" ht="17.25" spans="1:10">
       <c r="A13" s="3">
-        <v>11002</v>
+        <v>11001</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" s="11">
+        <v>3</v>
+      </c>
+      <c r="E13" s="10" t="s">
         <v>53</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="D13" s="10">
-        <v>2</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>55</v>
       </c>
       <c r="F13" s="4">
         <v>48004</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>26</v>
@@ -1825,7 +1879,7 @@
     </row>
     <row r="14" ht="17.25" spans="1:10">
       <c r="A14" s="3">
-        <v>11003</v>
+        <v>11002</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>56</v>
@@ -1833,69 +1887,75 @@
       <c r="C14" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="11">
         <v>2</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="E14" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14" s="4">
+        <v>48004</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" ht="17.25" spans="1:10">
+      <c r="A15" s="3">
+        <v>11003</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D15" s="11">
+        <v>2</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="F15" s="7">
         <v>48006</v>
       </c>
-      <c r="G14" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J14" s="11" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" s="2" customFormat="1" spans="1:10">
-      <c r="A15" s="2">
-        <v>12001</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C15" s="5" t="s">
+      <c r="G15" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="D15" s="12">
-        <v>2</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>64</v>
+      <c r="H15" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>20</v>
+      </c>
+      <c r="J15" s="12" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" spans="1:10">
       <c r="A16" s="2">
-        <v>12002</v>
+        <v>12001</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="D16" s="2">
-        <v>1</v>
-      </c>
-      <c r="E16" s="13" t="s">
+      <c r="D16" s="13">
+        <v>2</v>
+      </c>
+      <c r="E16" s="14" t="s">
         <v>66</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>20</v>
@@ -1903,59 +1963,59 @@
     </row>
     <row r="17" s="2" customFormat="1" spans="1:15">
       <c r="A17" s="2">
-        <v>12003</v>
+        <v>12002</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>68</v>
       </c>
       <c r="D17" s="2">
-        <v>2</v>
-      </c>
-      <c r="E17" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E17" s="14" t="s">
         <v>69</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="M17" s="2" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" spans="1:15">
       <c r="A18" s="2">
-        <v>12004</v>
+        <v>12003</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D18" s="2">
         <v>2</v>
       </c>
-      <c r="E18" s="13" t="s">
-        <v>75</v>
+      <c r="E18" s="14" t="s">
+        <v>72</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>20</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" spans="1:15">
       <c r="A19" s="2">
-        <v>12005</v>
+        <v>12004</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>76</v>
@@ -1966,95 +2026,118 @@
       <c r="D19" s="2">
         <v>2</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="14" t="s">
         <v>78</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="O19" s="2" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" spans="1:15">
       <c r="A20" s="2">
-        <v>12006</v>
+        <v>12005</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D20" s="2">
         <v>2</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>20</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" spans="1:15">
       <c r="A21" s="2">
-        <v>12007</v>
+        <v>12006</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D21" s="2">
-        <v>1</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>92</v>
+        <v>2</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>20</v>
       </c>
+      <c r="J21" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>92</v>
+      </c>
     </row>
-    <row r="22" spans="1:15">
-      <c r="A22" s="3">
-        <v>12101</v>
-      </c>
-      <c r="B22" s="3" t="s">
+    <row r="22" s="2" customFormat="1" spans="1:15">
+      <c r="A22" s="2">
+        <v>12007</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>93</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="2">
+        <v>1</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15">
+      <c r="A23" s="3">
+        <v>12101</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D23" s="3">
         <v>2</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>95</v>
+      <c r="E23" s="3" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -2067,12 +2150,13 @@
   <conditionalFormatting sqref="D7">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D8">
+  <conditionalFormatting sqref="D8:D9">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/slots/resources/sample/condition.xlsx
+++ b/slots/resources/sample/condition.xlsx
@@ -180,7 +180,7 @@
     <t>remainingAttempts</t>
   </si>
   <si>
-    <t>remainingAttempts(activity表中的ID,剩余次数)</t>
+    <t>remainingAttempts(activity表中的ID，要求剩余次数大于等于此值，此活动原因总次数)</t>
   </si>
   <si>
     <t>个人投注次数</t>
@@ -1551,7 +1551,7 @@
     <col min="2" max="2" width="19.5" style="3" customWidth="1"/>
     <col min="3" max="3" width="19.625" style="3" customWidth="1"/>
     <col min="4" max="4" width="17.625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="45.1416666666667" style="3" customWidth="1"/>
+    <col min="5" max="5" width="102.375" style="3" customWidth="1"/>
     <col min="6" max="6" width="21.375" style="3" customWidth="1"/>
     <col min="7" max="7" width="38.625" style="3" customWidth="1"/>
     <col min="8" max="8" width="17.125" style="3" customWidth="1"/>
@@ -1750,7 +1750,7 @@
         <v>38</v>
       </c>
       <c r="D9" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>39</v>

--- a/slots/resources/sample/condition.xlsx
+++ b/slots/resources/sample/condition.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="condition" sheetId="1" r:id="rId1"/>
@@ -28,40 +28,8 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Administrator</author>
-  </authors>
-  <commentList>
-    <comment ref="C1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-首字母小写</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="96">
   <si>
     <t>id</t>
   </si>
@@ -172,15 +140,6 @@
   </si>
   <si>
     <t>playerPhone</t>
-  </si>
-  <si>
-    <t>活动剩余参与次数</t>
-  </si>
-  <si>
-    <t>remainingAttempts</t>
-  </si>
-  <si>
-    <t>remainingAttempts(activity表中的ID，要求剩余次数大于等于此值，此活动原因总次数)</t>
   </si>
   <si>
     <t>个人投注次数</t>
@@ -523,7 +482,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -546,12 +505,6 @@
     </font>
     <font>
       <sz val="12"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF7030A0"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -709,17 +662,6 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="34">
@@ -1048,137 +990,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1206,22 +1148,19 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1544,14 +1483,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O23"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
     <col min="2" max="2" width="19.5" style="3" customWidth="1"/>
     <col min="3" max="3" width="19.625" style="3" customWidth="1"/>
     <col min="4" max="4" width="17.625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="102.375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="45.1416666666667" style="3" customWidth="1"/>
     <col min="6" max="6" width="21.375" style="3" customWidth="1"/>
     <col min="7" max="7" width="38.625" style="3" customWidth="1"/>
     <col min="8" max="8" width="17.125" style="3" customWidth="1"/>
@@ -1739,11 +1678,11 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="17.25" spans="1:10">
-      <c r="A9" s="1">
-        <v>5</v>
-      </c>
-      <c r="B9" s="1" t="s">
+    <row r="9" ht="17.25" spans="1:10">
+      <c r="A9" s="3">
+        <v>10001</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>37</v>
       </c>
       <c r="C9" s="5" t="s">
@@ -1755,36 +1694,43 @@
       <c r="E9" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F9" s="7"/>
-      <c r="G9" s="8"/>
+      <c r="F9" s="4">
+        <v>48003</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="I9" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" ht="17.25" spans="1:10">
       <c r="A10" s="3">
-        <v>10001</v>
+        <v>10002</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D10" s="3">
         <v>3</v>
       </c>
-      <c r="E10" s="10" t="s">
-        <v>42</v>
+      <c r="E10" s="9" t="s">
+        <v>44</v>
       </c>
       <c r="F10" s="4">
         <v>48003</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>26</v>
@@ -1792,7 +1738,7 @@
     </row>
     <row r="11" ht="17.25" spans="1:10">
       <c r="A11" s="3">
-        <v>10002</v>
+        <v>10003</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>45</v>
@@ -1800,20 +1746,20 @@
       <c r="C11" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="D11" s="3">
-        <v>3</v>
-      </c>
-      <c r="E11" s="10" t="s">
+      <c r="D11" s="10">
+        <v>4</v>
+      </c>
+      <c r="E11" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F11" s="4">
         <v>48003</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>26</v>
@@ -1821,7 +1767,7 @@
     </row>
     <row r="12" ht="17.25" spans="1:10">
       <c r="A12" s="3">
-        <v>10003</v>
+        <v>11001</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>48</v>
@@ -1829,20 +1775,20 @@
       <c r="C12" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D12" s="11">
-        <v>4</v>
-      </c>
-      <c r="E12" s="10" t="s">
+      <c r="D12" s="10">
+        <v>3</v>
+      </c>
+      <c r="E12" s="9" t="s">
         <v>50</v>
       </c>
       <c r="F12" s="4">
-        <v>48003</v>
+        <v>48004</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>26</v>
@@ -1850,28 +1796,28 @@
     </row>
     <row r="13" ht="17.25" spans="1:10">
       <c r="A13" s="3">
-        <v>11001</v>
+        <v>11002</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13" s="11">
-        <v>3</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="D13" s="10">
+        <v>2</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>55</v>
       </c>
       <c r="F13" s="4">
         <v>48004</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>26</v>
@@ -1879,7 +1825,7 @@
     </row>
     <row r="14" ht="17.25" spans="1:10">
       <c r="A14" s="3">
-        <v>11002</v>
+        <v>11003</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>56</v>
@@ -1887,75 +1833,69 @@
       <c r="C14" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="10">
         <v>2</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="4">
-        <v>48004</v>
+      <c r="F14" s="7">
+        <v>48006</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
-    <row r="15" ht="17.25" spans="1:10">
-      <c r="A15" s="3">
-        <v>11003</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>59</v>
+    <row r="15" s="2" customFormat="1" spans="1:10">
+      <c r="A15" s="2">
+        <v>12001</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D15" s="11">
+        <v>62</v>
+      </c>
+      <c r="D15" s="12">
         <v>2</v>
       </c>
-      <c r="E15" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="F15" s="7">
-        <v>48006</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>55</v>
+      <c r="E15" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="J15" s="12" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" spans="1:10">
       <c r="A16" s="2">
-        <v>12001</v>
+        <v>12002</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="D16" s="13">
-        <v>2</v>
-      </c>
-      <c r="E16" s="14" t="s">
+      <c r="D16" s="2">
+        <v>1</v>
+      </c>
+      <c r="E16" s="13" t="s">
         <v>66</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>20</v>
@@ -1963,59 +1903,59 @@
     </row>
     <row r="17" s="2" customFormat="1" spans="1:15">
       <c r="A17" s="2">
-        <v>12002</v>
+        <v>12003</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>68</v>
       </c>
       <c r="D17" s="2">
-        <v>1</v>
-      </c>
-      <c r="E17" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="E17" s="13" t="s">
         <v>69</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>20</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" spans="1:15">
       <c r="A18" s="2">
-        <v>12003</v>
+        <v>12004</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D18" s="2">
         <v>2</v>
       </c>
-      <c r="E18" s="14" t="s">
-        <v>72</v>
+      <c r="E18" s="13" t="s">
+        <v>75</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" spans="1:15">
       <c r="A19" s="2">
-        <v>12004</v>
+        <v>12005</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>76</v>
@@ -2026,118 +1966,95 @@
       <c r="D19" s="2">
         <v>2</v>
       </c>
-      <c r="E19" s="14" t="s">
+      <c r="E19" s="2" t="s">
         <v>78</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>20</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" spans="1:15">
       <c r="A20" s="2">
-        <v>12005</v>
+        <v>12006</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D20" s="2">
         <v>2</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>20</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" spans="1:15">
       <c r="A21" s="2">
-        <v>12006</v>
+        <v>12007</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D21" s="2">
-        <v>2</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>88</v>
+        <v>1</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>92</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>89</v>
+        <v>64</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J21" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="M21" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="O21" s="2" t="s">
-        <v>92</v>
-      </c>
     </row>
-    <row r="22" s="2" customFormat="1" spans="1:15">
-      <c r="A22" s="2">
-        <v>12007</v>
-      </c>
-      <c r="B22" s="2" t="s">
+    <row r="22" spans="1:15">
+      <c r="A22" s="3">
+        <v>12101</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>93</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="D22" s="2">
-        <v>1</v>
-      </c>
-      <c r="E22" s="14" t="s">
+      <c r="D22" s="3">
+        <v>2</v>
+      </c>
+      <c r="E22" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15">
-      <c r="A23" s="3">
-        <v>12101</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="D23" s="3">
-        <v>2</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -2150,13 +2067,12 @@
   <conditionalFormatting sqref="D7">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D8:D9">
+  <conditionalFormatting sqref="D8">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/slots/resources/sample/condition.xlsx
+++ b/slots/resources/sample/condition.xlsx
@@ -328,19 +328,14 @@
     <t>pay</t>
   </si>
   <si>
-    <t>个人累计充值</t>
+    <t>活动开始时个人累计充值</t>
   </si>
   <si>
     <t>totalRecharge</t>
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t>11002_总累计充值大于等于金额_</t>
+      <t>11002 活动开始后，总累计充值大于等于金额_</t>
     </r>
     <r>
       <rPr>
@@ -349,7 +344,7 @@
         <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
-      <t>渠道ID(0=默认所有)</t>
+      <t>渠道ID(0=默认所有)_活动ID</t>
     </r>
   </si>
   <si>
@@ -1178,7 +1173,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1213,6 +1208,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
@@ -1877,32 +1881,32 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" ht="17.25" spans="1:10">
-      <c r="A14" s="3">
+    <row r="14" s="1" customFormat="1" ht="17.25" spans="1:10">
+      <c r="A14" s="1">
         <v>11002</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="13">
         <v>2</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F14" s="7">
         <v>48004</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="G14" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="H14" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="I14" s="13" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1934,7 +1938,7 @@
       <c r="I15" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J15" s="12" t="s">
+      <c r="J15" s="15" t="s">
         <v>63</v>
       </c>
     </row>
@@ -1948,10 +1952,10 @@
       <c r="C16" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="D16" s="13">
+      <c r="D16" s="16">
         <v>2</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="E16" s="17" t="s">
         <v>66</v>
       </c>
       <c r="H16" s="2" t="s">
@@ -1974,7 +1978,7 @@
       <c r="D17" s="2">
         <v>1</v>
       </c>
-      <c r="E17" s="14" t="s">
+      <c r="E17" s="17" t="s">
         <v>69</v>
       </c>
       <c r="H17" s="2" t="s">
@@ -1997,7 +2001,7 @@
       <c r="D18" s="2">
         <v>2</v>
       </c>
-      <c r="E18" s="14" t="s">
+      <c r="E18" s="17" t="s">
         <v>72</v>
       </c>
       <c r="H18" s="2" t="s">
@@ -2026,7 +2030,7 @@
       <c r="D19" s="2">
         <v>2</v>
       </c>
-      <c r="E19" s="14" t="s">
+      <c r="E19" s="17" t="s">
         <v>78</v>
       </c>
       <c r="H19" s="2" t="s">
@@ -2113,7 +2117,7 @@
       <c r="D22" s="2">
         <v>1</v>
       </c>
-      <c r="E22" s="14" t="s">
+      <c r="E22" s="17" t="s">
         <v>95</v>
       </c>
       <c r="H22" s="2" t="s">

--- a/slots/resources/sample/condition.xlsx
+++ b/slots/resources/sample/condition.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="102">
   <si>
     <t>id</t>
   </si>
@@ -322,16 +322,16 @@
     </r>
   </si>
   <si>
-    <t>您的充值金额不足{0}，请稍后再试</t>
+    <t>您的充值金额不足%s，请稍后再试</t>
   </si>
   <si>
     <t>pay</t>
   </si>
   <si>
-    <t>活动开始时个人累计充值</t>
-  </si>
-  <si>
-    <t>totalRecharge</t>
+    <t>此活动开始时个人累计充值</t>
+  </si>
+  <si>
+    <t>activityTotalRecharge</t>
   </si>
   <si>
     <r>
@@ -344,7 +344,7 @@
         <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
-      <t>渠道ID(0=默认所有)_活动ID</t>
+      <t>渠道ID</t>
     </r>
   </si>
   <si>
@@ -373,10 +373,19 @@
     </r>
   </si>
   <si>
-    <t>您今日的充值金额不足{0}，请稍后再试</t>
+    <t>您今日的充值金额不足%s，请稍后再试</t>
   </si>
   <si>
     <t>AND(LEVEL(30), LEVEL(40))，or,not</t>
+  </si>
+  <si>
+    <t>账号个人累计充值</t>
+  </si>
+  <si>
+    <t>accountTotalRecharge</t>
+  </si>
+  <si>
+    <t>11004 账号个人累计充值（要求金额）</t>
   </si>
   <si>
     <t>个人有效下注</t>
@@ -1173,8 +1182,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1195,29 +1207,41 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
@@ -1548,169 +1572,169 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O23"/>
+  <dimension ref="A1:O24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="9" style="3"/>
-    <col min="2" max="2" width="19.5" style="3" customWidth="1"/>
-    <col min="3" max="3" width="19.625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="17.625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="102.375" style="3" customWidth="1"/>
-    <col min="6" max="6" width="21.375" style="3" customWidth="1"/>
-    <col min="7" max="7" width="38.625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="17.125" style="3" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="3"/>
+    <col min="1" max="1" width="9" style="4"/>
+    <col min="2" max="2" width="25.375" style="4" customWidth="1"/>
+    <col min="3" max="3" width="19.625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="17.625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="102.375" style="4" customWidth="1"/>
+    <col min="6" max="6" width="21.375" style="4" customWidth="1"/>
+    <col min="7" max="7" width="38.625" style="4" customWidth="1"/>
+    <col min="8" max="8" width="17.125" style="4" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4"/>
-      <c r="F1" s="3" t="s">
+      <c r="E1" s="5"/>
+      <c r="F1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4" t="s">
+      <c r="E2" s="5"/>
+      <c r="F2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" ht="17.25" spans="1:10">
-      <c r="A5" s="3">
+      <c r="A5" s="4">
         <v>1</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="4">
         <v>1</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="5">
         <v>48001</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I5" s="4" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="6" ht="17.25" spans="1:10">
-      <c r="A6" s="3">
+      <c r="A6" s="4">
         <v>2</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="4">
         <v>1</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="5">
         <v>48002</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="H6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="I6" s="4" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="7" ht="17.25" spans="1:10">
-      <c r="A7" s="3">
+      <c r="A7" s="4">
         <v>3</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="4">
         <v>1</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="5">
         <v>48001</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="H7" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="I7" s="4" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1721,25 +1745,25 @@
       <c r="B8" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="9">
         <v>1</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="10">
         <v>48005</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="G8" s="11" t="s">
         <v>35</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="I8" s="9" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1750,398 +1774,428 @@
       <c r="B9" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="9">
         <v>3</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="F9" s="7"/>
-      <c r="G9" s="8"/>
-      <c r="I9" s="3" t="s">
+      <c r="F9" s="10"/>
+      <c r="G9" s="11"/>
+      <c r="I9" s="9" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="10" ht="17.25" spans="1:10">
-      <c r="A10" s="3">
+      <c r="A10" s="4">
         <v>10001</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="4">
         <v>3</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="5">
         <v>48003</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="H10" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="I10" s="4" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="11" ht="17.25" spans="1:10">
-      <c r="A11" s="3">
+      <c r="A11" s="4">
         <v>10002</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="4">
         <v>3</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="5">
         <v>48003</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="H11" s="3" t="s">
+      <c r="H11" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="I11" s="3" t="s">
+      <c r="I11" s="4" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="12" ht="17.25" spans="1:10">
-      <c r="A12" s="3">
+      <c r="A12" s="4">
         <v>10003</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="14">
         <v>4</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="5">
         <v>48003</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="G12" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="H12" s="3" t="s">
+      <c r="H12" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="I12" s="4" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="13" ht="17.25" spans="1:10">
-      <c r="A13" s="3">
+      <c r="A13" s="4">
         <v>11001</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="14">
         <v>3</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="E13" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="5">
         <v>48004</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="G13" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H13" s="3" t="s">
+      <c r="H13" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="I13" s="3" t="s">
+      <c r="I13" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="17.25" spans="1:10">
-      <c r="A14" s="1">
+    <row r="14" s="2" customFormat="1" ht="17.25" spans="1:10">
+      <c r="A14" s="2">
         <v>11002</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="13">
+      <c r="D14" s="16">
         <v>2</v>
       </c>
-      <c r="E14" s="14" t="s">
+      <c r="E14" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14" s="18">
         <v>48004</v>
       </c>
-      <c r="G14" s="8" t="s">
+      <c r="G14" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="H14" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="I14" s="13" t="s">
-        <v>26</v>
+      <c r="I14" s="4" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="15" ht="17.25" spans="1:10">
-      <c r="A15" s="3">
+      <c r="A15" s="4">
         <v>11003</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="D15" s="11">
+      <c r="D15" s="14">
         <v>2</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="E15" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F15" s="18">
         <v>48006</v>
       </c>
-      <c r="G15" s="6" t="s">
+      <c r="G15" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="H15" s="3" t="s">
+      <c r="H15" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="I15" s="3" t="s">
+      <c r="I15" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J15" s="15" t="s">
+      <c r="J15" s="20" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="16" s="2" customFormat="1" spans="1:10">
-      <c r="A16" s="2">
+    <row r="16" customFormat="1" ht="17.25" spans="1:10">
+      <c r="A16" s="4">
+        <v>11004</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D16" s="14">
+        <v>1</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="F16" s="5">
+        <v>48004</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J16" s="20"/>
+    </row>
+    <row r="17" s="3" customFormat="1" spans="1:15">
+      <c r="A17" s="3">
         <v>12001</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D16" s="16">
+      <c r="B17" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D17" s="21">
         <v>2</v>
       </c>
-      <c r="E16" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="H16" s="2" t="s">
+      <c r="E17" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" s="3" customFormat="1" spans="1:15">
+      <c r="A18" s="3">
+        <v>12002</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="I16" s="3" t="s">
+      <c r="C18" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D18" s="3">
+        <v>1</v>
+      </c>
+      <c r="E18" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="I18" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="17" s="2" customFormat="1" spans="1:15">
-      <c r="A17" s="2">
-        <v>12002</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D17" s="2">
-        <v>1</v>
-      </c>
-      <c r="E17" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="I17" s="3" t="s">
+    <row r="19" s="3" customFormat="1" spans="1:15">
+      <c r="A19" s="3">
+        <v>12003</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D19" s="3">
+        <v>2</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I19" s="4" t="s">
         <v>20</v>
       </c>
+      <c r="J19" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>78</v>
+      </c>
     </row>
-    <row r="18" s="2" customFormat="1" spans="1:15">
-      <c r="A18" s="2">
-        <v>12003</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D18" s="2">
+    <row r="20" s="3" customFormat="1" spans="1:15">
+      <c r="A20" s="3">
+        <v>12004</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D20" s="3">
         <v>2</v>
       </c>
-      <c r="E18" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="I18" s="3" t="s">
+      <c r="E20" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I20" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J18" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>75</v>
-      </c>
     </row>
-    <row r="19" s="2" customFormat="1" spans="1:15">
-      <c r="A19" s="2">
-        <v>12004</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="D19" s="2">
+    <row r="21" s="3" customFormat="1" spans="1:15">
+      <c r="A21" s="3">
+        <v>12005</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D21" s="3">
         <v>2</v>
       </c>
-      <c r="E19" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="I19" s="3" t="s">
+      <c r="E21" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I21" s="4" t="s">
         <v>20</v>
       </c>
+      <c r="J21" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>88</v>
+      </c>
     </row>
-    <row r="20" s="2" customFormat="1" spans="1:15">
-      <c r="A20" s="2">
-        <v>12005</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="D20" s="2">
+    <row r="22" s="3" customFormat="1" spans="1:15">
+      <c r="A22" s="3">
+        <v>12006</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D22" s="3">
         <v>2</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="I20" s="3" t="s">
+      <c r="E22" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="I22" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J20" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="M20" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="O20" s="2" t="s">
-        <v>85</v>
+      <c r="J22" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>95</v>
       </c>
     </row>
-    <row r="21" s="2" customFormat="1" spans="1:15">
-      <c r="A21" s="2">
-        <v>12006</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="D21" s="2">
-        <v>2</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="M21" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="O21" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="22" s="2" customFormat="1" spans="1:15">
-      <c r="A22" s="2">
+    <row r="23" s="3" customFormat="1" spans="1:15">
+      <c r="A23" s="3">
         <v>12007</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="D22" s="2">
-        <v>1</v>
-      </c>
-      <c r="E22" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15">
-      <c r="A23" s="3">
-        <v>12101</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="6" t="s">
         <v>97</v>
       </c>
       <c r="D23" s="3">
+        <v>1</v>
+      </c>
+      <c r="E23" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15">
+      <c r="A24" s="4">
+        <v>12101</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D24" s="4">
         <v>2</v>
       </c>
-      <c r="E23" s="3" t="s">
-        <v>98</v>
+      <c r="E24" s="4" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/condition.xlsx
+++ b/slots/resources/sample/condition.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="105">
   <si>
     <t>id</t>
   </si>
@@ -335,6 +335,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>11002 活动开始后，总累计充值大于等于金额_</t>
     </r>
     <r>
@@ -355,11 +360,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
       <t>11003_当日累计充值大于等于金额_</t>
     </r>
     <r>
@@ -379,13 +379,33 @@
     <t>AND(LEVEL(30), LEVEL(40))，or,not</t>
   </si>
   <si>
+    <t>个人累计充值（功能开启时计数）</t>
+  </si>
+  <si>
+    <t>totalRecharge</t>
+  </si>
+  <si>
+    <r>
+      <t>11004 账号个人累计充值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>_渠道ID(0=默认所有)</t>
+    </r>
+  </si>
+  <si>
     <t>账号个人累计充值</t>
   </si>
   <si>
     <t>accountTotalRecharge</t>
   </si>
   <si>
-    <t>11004 账号个人累计充值（要求金额）</t>
+    <t>11005 账号个人累计充值（要求金额）</t>
   </si>
   <si>
     <t>个人有效下注</t>
@@ -715,12 +735,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1192,6 +1212,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1210,14 +1233,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
@@ -1244,6 +1261,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1572,169 +1592,169 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="9" style="4"/>
-    <col min="2" max="2" width="25.375" style="4" customWidth="1"/>
-    <col min="3" max="3" width="19.625" style="4" customWidth="1"/>
-    <col min="4" max="4" width="17.625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="102.375" style="4" customWidth="1"/>
-    <col min="6" max="6" width="21.375" style="4" customWidth="1"/>
-    <col min="7" max="7" width="38.625" style="4" customWidth="1"/>
-    <col min="8" max="8" width="17.125" style="4" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="4"/>
+    <col min="1" max="1" width="9" style="5"/>
+    <col min="2" max="2" width="31.625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="19.625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="17.625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="102.375" style="5" customWidth="1"/>
+    <col min="6" max="6" width="21.375" style="5" customWidth="1"/>
+    <col min="7" max="7" width="38.625" style="5" customWidth="1"/>
+    <col min="8" max="8" width="17.125" style="5" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5"/>
-      <c r="F1" s="4" t="s">
+      <c r="E1" s="6"/>
+      <c r="F1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5" t="s">
+      <c r="E2" s="6"/>
+      <c r="F2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" ht="17.25" spans="1:10">
-      <c r="A5" s="4">
+      <c r="A5" s="5">
         <v>1</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="5">
         <v>1</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="6">
         <v>48001</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="5" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="6" ht="17.25" spans="1:10">
-      <c r="A6" s="4">
+      <c r="A6" s="5">
         <v>2</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="5">
         <v>1</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="6">
         <v>48002</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="5" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="7" ht="17.25" spans="1:10">
-      <c r="A7" s="4">
+      <c r="A7" s="5">
         <v>3</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="5">
         <v>1</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="6">
         <v>48001</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="5" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1745,10 +1765,10 @@
       <c r="B8" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="1">
         <v>1</v>
       </c>
       <c r="E8" s="1" t="s">
@@ -1757,13 +1777,13 @@
       <c r="F8" s="10">
         <v>48005</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="G8" s="8" t="s">
         <v>35</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I8" s="9" t="s">
+      <c r="I8" s="1" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1774,134 +1794,134 @@
       <c r="B9" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="1">
         <v>3</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="11" t="s">
         <v>39</v>
       </c>
       <c r="F9" s="10"/>
-      <c r="G9" s="11"/>
-      <c r="I9" s="9" t="s">
+      <c r="G9" s="8"/>
+      <c r="I9" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="10" ht="17.25" spans="1:10">
-      <c r="A10" s="4">
+      <c r="A10" s="5">
         <v>10001</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="5">
         <v>3</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="E10" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10" s="6">
         <v>48003</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G10" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H10" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="5" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="11" ht="17.25" spans="1:10">
-      <c r="A11" s="4">
+      <c r="A11" s="5">
         <v>10002</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="5">
         <v>3</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="E11" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F11" s="6">
         <v>48003</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="H11" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="I11" s="5" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="12" ht="17.25" spans="1:10">
-      <c r="A12" s="4">
+      <c r="A12" s="5">
         <v>10003</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="13">
         <v>4</v>
       </c>
-      <c r="E12" s="13" t="s">
+      <c r="E12" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="6">
         <v>48003</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="G12" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="H12" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="I12" s="4" t="s">
+      <c r="I12" s="5" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="13" ht="17.25" spans="1:10">
-      <c r="A13" s="4">
+      <c r="A13" s="5">
         <v>11001</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="D13" s="14">
+      <c r="D13" s="13">
         <v>3</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="E13" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13" s="6">
         <v>48004</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="G13" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="H13" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="I13" s="5" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1912,290 +1932,320 @@
       <c r="B14" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="16">
+      <c r="D14" s="15">
         <v>2</v>
       </c>
-      <c r="E14" s="17" t="s">
+      <c r="E14" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="18">
+      <c r="F14" s="17">
         <v>48004</v>
       </c>
-      <c r="G14" s="19" t="s">
+      <c r="G14" s="18" t="s">
         <v>54</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="I14" s="4" t="s">
+      <c r="I14" s="5" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="15" ht="17.25" spans="1:10">
-      <c r="A15" s="4">
+      <c r="A15" s="5">
         <v>11003</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="D15" s="14">
+      <c r="D15" s="13">
         <v>2</v>
       </c>
-      <c r="E15" s="13" t="s">
+      <c r="E15" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="F15" s="18">
+      <c r="F15" s="17">
         <v>48006</v>
       </c>
-      <c r="G15" s="7" t="s">
+      <c r="G15" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="H15" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="I15" s="4" t="s">
+      <c r="I15" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="J15" s="20" t="s">
+      <c r="J15" s="19" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="16" customFormat="1" ht="17.25" spans="1:10">
-      <c r="A16" s="4">
+      <c r="A16" s="5">
         <v>11004</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D16" s="14">
+      <c r="D16" s="13">
+        <v>2</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="F16" s="6">
+        <v>48004</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="J16" s="19"/>
+    </row>
+    <row r="17" s="3" customFormat="1" ht="17.25" spans="1:15">
+      <c r="A17" s="2">
+        <v>11005</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="D17" s="15">
         <v>1</v>
       </c>
-      <c r="E16" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="F16" s="5">
+      <c r="E17" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="F17" s="17">
         <v>48004</v>
       </c>
-      <c r="G16" s="7" t="s">
+      <c r="G17" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="H17" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="I16" s="4" t="s">
+      <c r="I17" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="J16" s="20"/>
-    </row>
-    <row r="17" s="3" customFormat="1" spans="1:15">
-      <c r="A17" s="3">
+      <c r="J17" s="20"/>
+    </row>
+    <row r="18" s="4" customFormat="1" spans="1:15">
+      <c r="A18" s="4">
         <v>12001</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="D17" s="21">
+      <c r="B18" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D18" s="21">
         <v>2</v>
-      </c>
-      <c r="E17" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18" s="3" customFormat="1" spans="1:15">
-      <c r="A18" s="3">
-        <v>12002</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D18" s="3">
-        <v>1</v>
       </c>
       <c r="E18" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="H18" s="3" t="s">
+      <c r="H18" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" s="4" customFormat="1" spans="1:15">
+      <c r="A19" s="4">
+        <v>12002</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="I18" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="19" s="3" customFormat="1" spans="1:15">
-      <c r="A19" s="3">
-        <v>12003</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="D19" s="3">
-        <v>2</v>
+      <c r="D19" s="4">
+        <v>1</v>
       </c>
       <c r="E19" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="H19" s="3" t="s">
+      <c r="H19" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" s="4" customFormat="1" spans="1:15">
+      <c r="A20" s="4">
+        <v>12003</v>
+      </c>
+      <c r="B20" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="I19" s="4" t="s">
+      <c r="C20" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D20" s="4">
+        <v>2</v>
+      </c>
+      <c r="E20" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="I20" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="J19" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="20" s="3" customFormat="1" spans="1:15">
-      <c r="A20" s="3">
+      <c r="J20" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="M20" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="21" s="4" customFormat="1" spans="1:15">
+      <c r="A21" s="4">
         <v>12004</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B21" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D21" s="4">
+        <v>2</v>
+      </c>
+      <c r="E21" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="H21" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C20" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="D20" s="3">
+      <c r="I21" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" s="4" customFormat="1" spans="1:15">
+      <c r="A22" s="4">
+        <v>12005</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="D22" s="4">
         <v>2</v>
       </c>
-      <c r="E20" s="22" t="s">
-        <v>81</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I20" s="4" t="s">
+      <c r="E22" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="I22" s="5" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="21" s="3" customFormat="1" spans="1:15">
-      <c r="A21" s="3">
-        <v>12005</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="D21" s="3">
+      <c r="J22" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="M22" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="O22" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="23" s="4" customFormat="1" spans="1:15">
+      <c r="A23" s="4">
+        <v>12006</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="D23" s="4">
         <v>2</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I21" s="4" t="s">
+      <c r="E23" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="I23" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="22" s="3" customFormat="1" spans="1:15">
-      <c r="A22" s="3">
-        <v>12006</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="D22" s="3">
-        <v>2</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="23" s="3" customFormat="1" spans="1:15">
-      <c r="A23" s="3">
+      <c r="J23" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="M23" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="O23" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="24" s="4" customFormat="1" spans="1:15">
+      <c r="A24" s="4">
         <v>12007</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="D23" s="3">
-        <v>1</v>
-      </c>
-      <c r="E23" s="22" t="s">
-        <v>98</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15">
-      <c r="A24" s="4">
-        <v>12101</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="7" t="s">
         <v>100</v>
       </c>
       <c r="D24" s="4">
+        <v>1</v>
+      </c>
+      <c r="E24" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15">
+      <c r="A25" s="5">
+        <v>12101</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" s="5">
         <v>2</v>
       </c>
-      <c r="E24" s="4" t="s">
-        <v>101</v>
+      <c r="E25" s="5" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/slots/resources/sample/condition.xlsx
+++ b/slots/resources/sample/condition.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="condition" sheetId="1" r:id="rId1"/>
@@ -28,8 +28,40 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Administrator</author>
+  </authors>
+  <commentList>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+首字母小写</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="105">
   <si>
     <t>id</t>
   </si>
@@ -140,6 +172,15 @@
   </si>
   <si>
     <t>playerPhone</t>
+  </si>
+  <si>
+    <t>活动剩余参与次数</t>
+  </si>
+  <si>
+    <t>remainingAttempts</t>
+  </si>
+  <si>
+    <t>remainingAttempts(activity表中的ID，要求剩余次数大于等于此值，此活动原因总次数)</t>
   </si>
   <si>
     <t>个人投注次数</t>
@@ -281,16 +322,16 @@
     </r>
   </si>
   <si>
-    <t>您的充值金额不足{0}，请稍后再试</t>
+    <t>您的充值金额不足%s，请稍后再试</t>
   </si>
   <si>
     <t>pay</t>
   </si>
   <si>
-    <t>个人累计充值</t>
-  </si>
-  <si>
-    <t>totalRecharge</t>
+    <t>此活动开始时个人累计充值</t>
+  </si>
+  <si>
+    <t>activityTotalRecharge</t>
   </si>
   <si>
     <r>
@@ -299,7 +340,7 @@
         <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
-      <t>11002_总累计充值大于等于金额_</t>
+      <t>11002 活动开始后，总累计充值大于等于金额_</t>
     </r>
     <r>
       <rPr>
@@ -308,7 +349,7 @@
         <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
-      <t>渠道ID(0=默认所有)</t>
+      <t>渠道ID</t>
     </r>
   </si>
   <si>
@@ -319,11 +360,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
       <t>11003_当日累计充值大于等于金额_</t>
     </r>
     <r>
@@ -337,10 +373,39 @@
     </r>
   </si>
   <si>
-    <t>您今日的充值金额不足{0}，请稍后再试</t>
+    <t>您今日的充值金额不足%s，请稍后再试</t>
   </si>
   <si>
     <t>AND(LEVEL(30), LEVEL(40))，or,not</t>
+  </si>
+  <si>
+    <t>个人累计充值（功能开启时计数）</t>
+  </si>
+  <si>
+    <t>totalRecharge</t>
+  </si>
+  <si>
+    <r>
+      <t>11004 账号个人累计充值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>_渠道ID(0=默认所有)</t>
+    </r>
+  </si>
+  <si>
+    <t>账号个人累计充值</t>
+  </si>
+  <si>
+    <t>accountTotalRecharge</t>
+  </si>
+  <si>
+    <t>11005 账号个人累计充值（要求金额）</t>
   </si>
   <si>
     <t>个人有效下注</t>
@@ -482,7 +547,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -505,6 +570,12 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF7030A0"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -662,6 +733,17 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="34">
@@ -990,141 +1072,147 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1142,25 +1230,46 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1483,169 +1592,169 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O22"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="9" style="3"/>
-    <col min="2" max="2" width="19.5" style="3" customWidth="1"/>
-    <col min="3" max="3" width="19.625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="17.625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="45.1416666666667" style="3" customWidth="1"/>
-    <col min="6" max="6" width="21.375" style="3" customWidth="1"/>
-    <col min="7" max="7" width="38.625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="17.125" style="3" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="3"/>
+    <col min="1" max="1" width="9" style="5"/>
+    <col min="2" max="2" width="31.625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="19.625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="17.625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="102.375" style="5" customWidth="1"/>
+    <col min="6" max="6" width="21.375" style="5" customWidth="1"/>
+    <col min="7" max="7" width="38.625" style="5" customWidth="1"/>
+    <col min="8" max="8" width="17.125" style="5" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4"/>
-      <c r="F1" s="3" t="s">
+      <c r="E1" s="6"/>
+      <c r="F1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4" t="s">
+      <c r="E2" s="6"/>
+      <c r="F2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" ht="17.25" spans="1:10">
-      <c r="A5" s="3">
+      <c r="A5" s="5">
         <v>1</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="5">
         <v>1</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="6">
         <v>48001</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I5" s="5" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="6" ht="17.25" spans="1:10">
-      <c r="A6" s="3">
+      <c r="A6" s="5">
         <v>2</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="5">
         <v>1</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="6">
         <v>48002</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="H6" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="I6" s="5" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="7" ht="17.25" spans="1:10">
-      <c r="A7" s="3">
+      <c r="A7" s="5">
         <v>3</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="5">
         <v>1</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="6">
         <v>48001</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="H7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="I7" s="5" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1656,16 +1765,16 @@
       <c r="B8" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="1">
         <v>1</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="10">
         <v>48005</v>
       </c>
       <c r="G8" s="8" t="s">
@@ -1674,387 +1783,469 @@
       <c r="H8" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="I8" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" ht="17.25" spans="1:10">
-      <c r="A9" s="3">
+    <row r="9" s="1" customFormat="1" ht="17.25" spans="1:10">
+      <c r="A9" s="1">
+        <v>5</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="1">
+        <v>3</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="10"/>
+      <c r="G9" s="8"/>
+      <c r="I9" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" ht="17.25" spans="1:10">
+      <c r="A10" s="5">
         <v>10001</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" s="3">
+      <c r="B10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="5">
         <v>3</v>
       </c>
-      <c r="E9" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" s="4">
+      <c r="E10" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" s="6">
         <v>48003</v>
       </c>
-      <c r="G9" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="I9" s="3" t="s">
+      <c r="G10" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="I10" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="10" ht="17.25" spans="1:10">
-      <c r="A10" s="3">
+    <row r="11" ht="17.25" spans="1:10">
+      <c r="A11" s="5">
         <v>10002</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" s="5" t="s">
+      <c r="B11" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="5">
+        <v>3</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F11" s="6">
+        <v>48003</v>
+      </c>
+      <c r="G11" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="3">
+      <c r="H11" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" ht="17.25" spans="1:10">
+      <c r="A12" s="5">
+        <v>10003</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="13">
+        <v>4</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="F12" s="6">
+        <v>48003</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" ht="17.25" spans="1:10">
+      <c r="A13" s="5">
+        <v>11001</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" s="13">
         <v>3</v>
       </c>
-      <c r="E10" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="F10" s="4">
-        <v>48003</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="I10" s="3" t="s">
+      <c r="E13" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" s="6">
+        <v>48004</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="I13" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="11" ht="17.25" spans="1:10">
-      <c r="A11" s="3">
-        <v>10003</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" s="10">
-        <v>4</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="F11" s="4">
-        <v>48003</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" ht="17.25" spans="1:10">
-      <c r="A12" s="3">
-        <v>11001</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D12" s="10">
-        <v>3</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="F12" s="4">
+    <row r="14" s="2" customFormat="1" ht="17.25" spans="1:10">
+      <c r="A14" s="2">
+        <v>11002</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" s="15">
+        <v>2</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="F14" s="17">
         <v>48004</v>
       </c>
-      <c r="G12" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" ht="17.25" spans="1:10">
-      <c r="A13" s="3">
-        <v>11002</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13" s="5" t="s">
+      <c r="G14" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="D13" s="10">
+      <c r="H14" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" ht="17.25" spans="1:10">
+      <c r="A15" s="5">
+        <v>11003</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D15" s="13">
         <v>2</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E15" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="F15" s="17">
+        <v>48006</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="H15" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="F13" s="4">
+      <c r="I15" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="J15" s="19" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" customFormat="1" ht="17.25" spans="1:10">
+      <c r="A16" s="5">
+        <v>11004</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D16" s="13">
+        <v>2</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="F16" s="6">
         <v>48004</v>
       </c>
-      <c r="G13" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" ht="17.25" spans="1:10">
-      <c r="A14" s="3">
-        <v>11003</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D14" s="10">
-        <v>2</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="F14" s="7">
-        <v>48006</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="I14" s="3" t="s">
+      <c r="G16" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="I16" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="J14" s="11" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" s="2" customFormat="1" spans="1:10">
-      <c r="A15" s="2">
-        <v>12001</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D15" s="12">
-        <v>2</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" s="2" customFormat="1" spans="1:10">
-      <c r="A16" s="2">
-        <v>12002</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D16" s="2">
-        <v>1</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" s="2" customFormat="1" spans="1:15">
+      <c r="J16" s="19"/>
+    </row>
+    <row r="17" s="3" customFormat="1" ht="17.25" spans="1:15">
       <c r="A17" s="2">
-        <v>12003</v>
+        <v>11005</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="15">
+        <v>1</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="F17" s="17">
+        <v>48004</v>
+      </c>
+      <c r="G17" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J17" s="20"/>
+    </row>
+    <row r="18" s="4" customFormat="1" spans="1:15">
+      <c r="A18" s="4">
+        <v>12001</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D18" s="21">
         <v>2</v>
       </c>
-      <c r="E17" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="H17" s="2" t="s">
+      <c r="E18" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" s="4" customFormat="1" spans="1:15">
+      <c r="A19" s="4">
+        <v>12002</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="I17" s="3" t="s">
+      <c r="C19" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D19" s="4">
+        <v>1</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I19" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="J17" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="M17" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="18" s="2" customFormat="1" spans="1:15">
-      <c r="A18" s="2">
+    </row>
+    <row r="20" s="4" customFormat="1" spans="1:15">
+      <c r="A20" s="4">
+        <v>12003</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D20" s="4">
+        <v>2</v>
+      </c>
+      <c r="E20" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="M20" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="21" s="4" customFormat="1" spans="1:15">
+      <c r="A21" s="4">
         <v>12004</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B21" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D21" s="4">
+        <v>2</v>
+      </c>
+      <c r="E21" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" s="4" customFormat="1" spans="1:15">
+      <c r="A22" s="4">
+        <v>12005</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="D22" s="4">
+        <v>2</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="M22" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="O22" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="23" s="4" customFormat="1" spans="1:15">
+      <c r="A23" s="4">
+        <v>12006</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="D23" s="4">
+        <v>2</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="M23" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="O23" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="24" s="4" customFormat="1" spans="1:15">
+      <c r="A24" s="4">
+        <v>12007</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="D24" s="4">
+        <v>1</v>
+      </c>
+      <c r="E24" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="H24" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="C18" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D18" s="2">
+      <c r="I24" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15">
+      <c r="A25" s="5">
+        <v>12101</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" s="5">
         <v>2</v>
       </c>
-      <c r="E18" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="19" s="2" customFormat="1" spans="1:15">
-      <c r="A19" s="2">
-        <v>12005</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="D19" s="2">
-        <v>2</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="O19" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="20" s="2" customFormat="1" spans="1:15">
-      <c r="A20" s="2">
-        <v>12006</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="D20" s="2">
-        <v>2</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="M20" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="O20" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="21" s="2" customFormat="1" spans="1:15">
-      <c r="A21" s="2">
-        <v>12007</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="D21" s="2">
-        <v>1</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15">
-      <c r="A22" s="3">
-        <v>12101</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="D22" s="3">
-        <v>2</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>95</v>
+      <c r="E25" s="5" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -2067,12 +2258,13 @@
   <conditionalFormatting sqref="D7">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D8">
+  <conditionalFormatting sqref="D8:D9">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/slots/resources/sample/condition.xlsx
+++ b/slots/resources/sample/condition.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="condition" sheetId="1" r:id="rId1"/>
@@ -28,40 +28,8 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Administrator</author>
-  </authors>
-  <commentList>
-    <comment ref="C1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-首字母小写</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="96">
   <si>
     <t>id</t>
   </si>
@@ -172,15 +140,6 @@
   </si>
   <si>
     <t>playerPhone</t>
-  </si>
-  <si>
-    <t>活动剩余参与次数</t>
-  </si>
-  <si>
-    <t>remainingAttempts</t>
-  </si>
-  <si>
-    <t>remainingAttempts(activity表中的ID，要求剩余次数大于等于此值，此活动原因总次数)</t>
   </si>
   <si>
     <t>个人投注次数</t>
@@ -322,16 +281,16 @@
     </r>
   </si>
   <si>
-    <t>您的充值金额不足%s，请稍后再试</t>
+    <t>您的充值金额不足{0}，请稍后再试</t>
   </si>
   <si>
     <t>pay</t>
   </si>
   <si>
-    <t>此活动开始时个人累计充值</t>
-  </si>
-  <si>
-    <t>activityTotalRecharge</t>
+    <t>个人累计充值</t>
+  </si>
+  <si>
+    <t>totalRecharge</t>
   </si>
   <si>
     <r>
@@ -340,7 +299,7 @@
         <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
-      <t>11002 活动开始后，总累计充值大于等于金额_</t>
+      <t>11002_总累计充值大于等于金额_</t>
     </r>
     <r>
       <rPr>
@@ -349,7 +308,7 @@
         <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
-      <t>渠道ID</t>
+      <t>渠道ID(0=默认所有)</t>
     </r>
   </si>
   <si>
@@ -360,6 +319,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>11003_当日累计充值大于等于金额_</t>
     </r>
     <r>
@@ -373,39 +337,10 @@
     </r>
   </si>
   <si>
-    <t>您今日的充值金额不足%s，请稍后再试</t>
+    <t>您今日的充值金额不足{0}，请稍后再试</t>
   </si>
   <si>
     <t>AND(LEVEL(30), LEVEL(40))，or,not</t>
-  </si>
-  <si>
-    <t>个人累计充值（功能开启时计数）</t>
-  </si>
-  <si>
-    <t>totalRecharge</t>
-  </si>
-  <si>
-    <r>
-      <t>11004 账号个人累计充值</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t>_渠道ID(0=默认所有)</t>
-    </r>
-  </si>
-  <si>
-    <t>账号个人累计充值</t>
-  </si>
-  <si>
-    <t>accountTotalRecharge</t>
-  </si>
-  <si>
-    <t>11005 账号个人累计充值（要求金额）</t>
   </si>
   <si>
     <t>个人有效下注</t>
@@ -547,7 +482,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -570,12 +505,6 @@
     </font>
     <font>
       <sz val="12"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF7030A0"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -733,17 +662,6 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="34">
@@ -1072,147 +990,141 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1230,46 +1142,25 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1592,169 +1483,169 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O25"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="9" style="5"/>
-    <col min="2" max="2" width="31.625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="19.625" style="5" customWidth="1"/>
-    <col min="4" max="4" width="17.625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="102.375" style="5" customWidth="1"/>
-    <col min="6" max="6" width="21.375" style="5" customWidth="1"/>
-    <col min="7" max="7" width="38.625" style="5" customWidth="1"/>
-    <col min="8" max="8" width="17.125" style="5" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="5"/>
+    <col min="1" max="1" width="9" style="3"/>
+    <col min="2" max="2" width="19.5" style="3" customWidth="1"/>
+    <col min="3" max="3" width="19.625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="17.625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="45.1416666666667" style="3" customWidth="1"/>
+    <col min="6" max="6" width="21.375" style="3" customWidth="1"/>
+    <col min="7" max="7" width="38.625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="17.125" style="3" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6"/>
-      <c r="F1" s="5" t="s">
+      <c r="E1" s="4"/>
+      <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6" t="s">
+      <c r="E2" s="4"/>
+      <c r="F2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" ht="17.25" spans="1:10">
-      <c r="A5" s="5">
+      <c r="A5" s="3">
         <v>1</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="3">
         <v>1</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="4">
         <v>48001</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="3" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="6" ht="17.25" spans="1:10">
-      <c r="A6" s="5">
+      <c r="A6" s="3">
         <v>2</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="3">
         <v>1</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="4">
         <v>48002</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="I6" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="7" ht="17.25" spans="1:10">
-      <c r="A7" s="5">
+      <c r="A7" s="3">
         <v>3</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="3">
         <v>1</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="4">
         <v>48001</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="H7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="I7" s="3" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1765,16 +1656,16 @@
       <c r="B8" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" s="3">
         <v>1</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="7">
         <v>48005</v>
       </c>
       <c r="G8" s="8" t="s">
@@ -1783,469 +1674,387 @@
       <c r="H8" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="I8" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="17.25" spans="1:10">
-      <c r="A9" s="1">
-        <v>5</v>
-      </c>
-      <c r="B9" s="1" t="s">
+    <row r="9" ht="17.25" spans="1:10">
+      <c r="A9" s="3">
+        <v>10001</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" s="3">
         <v>3</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F9" s="10"/>
-      <c r="G9" s="8"/>
-      <c r="I9" s="1" t="s">
-        <v>20</v>
+      <c r="F9" s="4">
+        <v>48003</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="10" ht="17.25" spans="1:10">
-      <c r="A10" s="5">
-        <v>10001</v>
-      </c>
-      <c r="B10" s="5" t="s">
+      <c r="A10" s="3">
+        <v>10002</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="3">
+        <v>3</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10" s="4">
+        <v>48003</v>
+      </c>
+      <c r="G10" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="H10" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="5">
-        <v>3</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="F10" s="6">
-        <v>48003</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="I10" s="5" t="s">
+      <c r="I10" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="11" ht="17.25" spans="1:10">
-      <c r="A11" s="5">
-        <v>10002</v>
-      </c>
-      <c r="B11" s="5" t="s">
+      <c r="A11" s="3">
+        <v>10003</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="D11" s="5">
-        <v>3</v>
-      </c>
-      <c r="E11" s="12" t="s">
+      <c r="D11" s="10">
+        <v>4</v>
+      </c>
+      <c r="E11" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="4">
         <v>48003</v>
       </c>
-      <c r="G11" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="I11" s="5" t="s">
+      <c r="G11" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="12" ht="17.25" spans="1:10">
-      <c r="A12" s="5">
-        <v>10003</v>
-      </c>
-      <c r="B12" s="5" t="s">
+      <c r="A12" s="3">
+        <v>11001</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D12" s="13">
-        <v>4</v>
-      </c>
-      <c r="E12" s="12" t="s">
+      <c r="D12" s="10">
+        <v>3</v>
+      </c>
+      <c r="E12" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="F12" s="6">
-        <v>48003</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="I12" s="5" t="s">
+      <c r="F12" s="4">
+        <v>48004</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="13" ht="17.25" spans="1:10">
-      <c r="A13" s="5">
-        <v>11001</v>
-      </c>
-      <c r="B13" s="5" t="s">
+      <c r="A13" s="3">
+        <v>11002</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" s="10">
+        <v>2</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" s="4">
+        <v>48004</v>
+      </c>
+      <c r="G13" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="H13" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D13" s="13">
-        <v>3</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="F13" s="6">
-        <v>48004</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="I13" s="5" t="s">
+      <c r="I13" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="14" s="2" customFormat="1" ht="17.25" spans="1:10">
-      <c r="A14" s="2">
-        <v>11002</v>
-      </c>
-      <c r="B14" s="2" t="s">
+    <row r="14" ht="17.25" spans="1:10">
+      <c r="A14" s="3">
+        <v>11003</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="15">
+      <c r="D14" s="10">
         <v>2</v>
       </c>
-      <c r="E14" s="16" t="s">
+      <c r="E14" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="17">
-        <v>48004</v>
-      </c>
-      <c r="G14" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="I14" s="5" t="s">
+      <c r="F14" s="7">
+        <v>48006</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>20</v>
       </c>
+      <c r="J14" s="11" t="s">
+        <v>60</v>
+      </c>
     </row>
-    <row r="15" ht="17.25" spans="1:10">
-      <c r="A15" s="5">
-        <v>11003</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="D15" s="13">
+    <row r="15" s="2" customFormat="1" spans="1:10">
+      <c r="A15" s="2">
+        <v>12001</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D15" s="12">
         <v>2</v>
       </c>
-      <c r="E15" s="12" t="s">
+      <c r="E15" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" s="2" customFormat="1" spans="1:10">
+      <c r="A16" s="2">
+        <v>12002</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="F15" s="17">
-        <v>48006</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="I15" s="5" t="s">
+      <c r="C16" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D16" s="2">
+        <v>1</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J15" s="19" t="s">
-        <v>63</v>
-      </c>
     </row>
-    <row r="16" customFormat="1" ht="17.25" spans="1:10">
-      <c r="A16" s="5">
-        <v>11004</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="D16" s="13">
-        <v>2</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="F16" s="6">
-        <v>48004</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="J16" s="19"/>
-    </row>
-    <row r="17" s="3" customFormat="1" ht="17.25" spans="1:15">
+    <row r="17" s="2" customFormat="1" spans="1:15">
       <c r="A17" s="2">
-        <v>11005</v>
+        <v>12003</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="14" t="s">
+      <c r="C17" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="D17" s="15">
+      <c r="D17" s="2">
+        <v>2</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18" s="2" customFormat="1" spans="1:15">
+      <c r="A18" s="2">
+        <v>12004</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D18" s="2">
+        <v>2</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" spans="1:15">
+      <c r="A19" s="2">
+        <v>12005</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D19" s="2">
+        <v>2</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1" spans="1:15">
+      <c r="A20" s="2">
+        <v>12006</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D20" s="2">
+        <v>2</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" spans="1:15">
+      <c r="A21" s="2">
+        <v>12007</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D21" s="2">
         <v>1</v>
       </c>
-      <c r="E17" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="F17" s="17">
-        <v>48004</v>
-      </c>
-      <c r="G17" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="I17" s="2" t="s">
+      <c r="E21" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J17" s="20"/>
     </row>
-    <row r="18" s="4" customFormat="1" spans="1:15">
-      <c r="A18" s="4">
-        <v>12001</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="D18" s="21">
+    <row r="22" spans="1:15">
+      <c r="A22" s="3">
+        <v>12101</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D22" s="3">
         <v>2</v>
       </c>
-      <c r="E18" s="22" t="s">
-        <v>72</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="I18" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="19" s="4" customFormat="1" spans="1:15">
-      <c r="A19" s="4">
-        <v>12002</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="D19" s="4">
-        <v>1</v>
-      </c>
-      <c r="E19" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" s="4" customFormat="1" spans="1:15">
-      <c r="A20" s="4">
-        <v>12003</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="D20" s="4">
-        <v>2</v>
-      </c>
-      <c r="E20" s="22" t="s">
-        <v>78</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="I20" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="M20" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="21" s="4" customFormat="1" spans="1:15">
-      <c r="A21" s="4">
-        <v>12004</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="D21" s="4">
-        <v>2</v>
-      </c>
-      <c r="E21" s="22" t="s">
-        <v>84</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="I21" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" s="4" customFormat="1" spans="1:15">
-      <c r="A22" s="4">
-        <v>12005</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="D22" s="4">
-        <v>2</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="I22" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="M22" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="O22" s="4" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="23" s="4" customFormat="1" spans="1:15">
-      <c r="A23" s="4">
-        <v>12006</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="D23" s="4">
-        <v>2</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="H23" s="4" t="s">
+      <c r="E22" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="I23" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="J23" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="M23" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="O23" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="24" s="4" customFormat="1" spans="1:15">
-      <c r="A24" s="4">
-        <v>12007</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="D24" s="4">
-        <v>1</v>
-      </c>
-      <c r="E24" s="22" t="s">
-        <v>101</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="I24" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15">
-      <c r="A25" s="5">
-        <v>12101</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="D25" s="5">
-        <v>2</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -2258,13 +2067,12 @@
   <conditionalFormatting sqref="D7">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D8:D9">
+  <conditionalFormatting sqref="D8">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
